--- a/2026/BELGRANO 1646/ENERO/Enero-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/ENERO/Enero-BLG1646.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELGRANO 1646\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\BELGRANO 1646\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4619159F-9CBB-4B73-AD4F-30DAF12C41B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F706743-1F45-493E-9E13-70E30369A3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$126</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="177">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -478,9 +478,6 @@
     <t>Contessi - Mantenimiento de ascensores</t>
   </si>
   <si>
-    <t>Subidos en jun de 2025</t>
-  </si>
-  <si>
     <t>BALBOA, ARIEL</t>
   </si>
   <si>
@@ -523,55 +520,18 @@
     <t>Energroup - SERVICE DE MANTENIMIENTO PREVENTIVO</t>
   </si>
   <si>
-    <t>Las expensas extraordinarias ascendieron a un total de $2.900.000. Sin embargo, considerando que pasar de un prorrateo de $450.000 a dicho monto implicaría un incremento significativo en el valor final de las expensas, se resolvió distribuir este importe en tres cuotas.
-Por lo tanto, en el presente período se prorratea una tercera parte del monto total correspondiente a las extraordinarias, con el fin de mantener un equilibrio en los valores a abonar.</t>
-  </si>
-  <si>
-    <t>Debito 12/11</t>
-  </si>
-  <si>
     <t xml:space="preserve">Numero 1859135 Debito automatico </t>
   </si>
   <si>
-    <t>Debito 04/12</t>
-  </si>
-  <si>
-    <t>Mozart SRL - Recarga de matafuegos y prueba hidraulica</t>
-  </si>
-  <si>
-    <t>Debito 30/12</t>
-  </si>
-  <si>
-    <t>Fumigacion 22/12</t>
-  </si>
-  <si>
     <t>Debito 26/12</t>
   </si>
   <si>
-    <t>Reemplazo Sr. Diego - Vacaciones - Sra. Monica Gorosito</t>
-  </si>
-  <si>
-    <t>Sr. Antonio piletero</t>
-  </si>
-  <si>
-    <t>Ferreteria el herrero - compra de insumos</t>
-  </si>
-  <si>
-    <t>Alterini Guido - Puesta a punto de jardineria</t>
-  </si>
-  <si>
-    <t>Vea - Compra canasta navideña</t>
-  </si>
-  <si>
     <t>SEGURO OBLIGATORIO SR DIEGO BRITEZ FEDERACION PATRONAL DEBITO AUTOMATICO</t>
   </si>
   <si>
     <t>Macarena</t>
   </si>
   <si>
-    <t xml:space="preserve">Seguro Sra. Monica </t>
-  </si>
-  <si>
     <t>VTO: 16/02</t>
   </si>
   <si>
@@ -588,6 +548,51 @@
   </si>
   <si>
     <t>Contessi - Cambio de tubos led ascensor N2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debito </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fumigacion </t>
+  </si>
+  <si>
+    <t>Servisur - Materiales y mano de obra de reemplazo de termica 10a</t>
+  </si>
+  <si>
+    <t>Servisur - 6 plafones en escalera y pasillo - Colocacion y compra de materiales</t>
+  </si>
+  <si>
+    <t>Balcazza Leonardo - Trabajo y reparacion de durlock - Ya abonado por Sr. Simonassi</t>
+  </si>
+  <si>
+    <t>Balcazza Leonardo - Trabajos de baranda, terrazas, pileta, sellado de singueria, pintado con epoxi negro - Material y mano de obra</t>
+  </si>
+  <si>
+    <t>Subidos en en3r0 de 2026</t>
+  </si>
+  <si>
+    <t>Contessi - Provision y colocacion de 40lts de aceite hidraulico en sede de monta auto</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Montoya Alejandra - Para pileta: cloro, clarificador, alguicida y regulador de PH</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ, JORGE AGUSTIN</t>
+  </si>
+  <si>
+    <t>Sr. Matias Buldo - Transporte y carga de combustible - Pago efectivo</t>
+  </si>
+  <si>
+    <t>Poda de arbol en vereda - Alterini Guido - Jardineria</t>
+  </si>
+  <si>
+    <t>Sur Energy Lanus- Compra de combustible - 12/01</t>
+  </si>
+  <si>
+    <t>Sur Energy Lanus- Compra de combustible - 19/01</t>
+  </si>
+  <si>
+    <t>Sur Energy Lanus- Compra de combustible - 21/01</t>
   </si>
 </sst>
 </file>
@@ -605,7 +610,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -776,6 +781,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1315,7 +1328,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
@@ -1590,14 +1603,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1673,93 +1696,117 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1784,7 +1831,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2150,24 +2202,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N130"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N136"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8"/>
       <c r="B1" s="96" t="s">
         <v>118</v>
@@ -2176,7 +2228,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="63"/>
       <c r="B2" s="64" t="s">
         <v>0</v>
@@ -2185,7 +2237,7 @@
       <c r="D2" s="64"/>
       <c r="E2" s="65"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="66"/>
       <c r="B3" s="67" t="s">
         <v>88</v>
@@ -2194,7 +2246,7 @@
       <c r="D3" s="67"/>
       <c r="E3" s="68"/>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="66"/>
       <c r="B4" s="67" t="s">
         <v>89</v>
@@ -2203,20 +2255,20 @@
       <c r="D4" s="67"/>
       <c r="E4" s="68"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="70" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D5" s="70"/>
       <c r="E5" s="71"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="66" t="s">
         <v>99</v>
       </c>
@@ -2225,7 +2277,7 @@
       <c r="D6" s="67"/>
       <c r="E6" s="68"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="69" t="s">
         <v>98</v>
       </c>
@@ -2234,37 +2286,37 @@
       <c r="D7" s="70"/>
       <c r="E7" s="71"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="200" t="s">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="204" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="201"/>
-      <c r="D14" s="202"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="203"/>
-      <c r="C15" s="204"/>
-      <c r="D15" s="205"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="203"/>
-      <c r="C16" s="204"/>
-      <c r="D16" s="205"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="206"/>
-      <c r="C17" s="207"/>
-      <c r="D17" s="208"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="205"/>
+      <c r="D14" s="206"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="207"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="209"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="207"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="209"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="210"/>
+      <c r="C17" s="211"/>
+      <c r="D17" s="212"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="60" t="s">
         <v>86</v>
       </c>
@@ -2278,93 +2330,88 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="119" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="125"/>
       <c r="E22" s="170"/>
       <c r="F22" s="170"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="119" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="193">
-        <v>1512458.96</v>
+      <c r="D23" s="192">
+        <v>1434809.5</v>
       </c>
       <c r="E23" s="129">
         <f>D23*91.91%</f>
-        <v>1390101.0301359999</v>
+        <v>1318733.4114499998</v>
       </c>
       <c r="F23" s="129">
         <f>D23*8.09%</f>
-        <v>122357.92986399999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>116076.08855</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="119" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="193">
-        <v>-328959.83</v>
+      <c r="D24" s="192">
+        <v>-312071.07</v>
       </c>
       <c r="E24" s="129">
         <f t="shared" ref="E24:E26" si="0">D24*91.91%</f>
-        <v>-302346.97975299996</v>
+        <v>-286824.52043699997</v>
       </c>
       <c r="F24" s="129">
         <f t="shared" ref="F24:F26" si="1">D24*8.09%</f>
-        <v>-26612.850247000002</v>
+        <v>-25246.549563</v>
       </c>
       <c r="G24" s="107"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="119" t="s">
         <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="193">
-        <v>0.87</v>
+      <c r="D25" s="192">
+        <v>0.56999999999999995</v>
       </c>
       <c r="E25" s="129">
         <f t="shared" si="0"/>
-        <v>0.79961699999999991</v>
+        <v>0.52388699999999988</v>
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>7.0383000000000001E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="119" t="s">
-        <v>109</v>
-      </c>
+        <v>4.6112999999999994E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="119"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="193">
-        <f>695568</f>
-        <v>695568</v>
-      </c>
+      <c r="D26" s="192"/>
       <c r="E26" s="129">
         <f t="shared" si="0"/>
-        <v>639296.54879999999</v>
+        <v>0</v>
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>56271.451200000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="94" t="s">
         <v>3</v>
       </c>
@@ -2372,32 +2419,32 @@
       <c r="C27" s="94"/>
       <c r="D27" s="106">
         <f>SUM(D23:D26)</f>
-        <v>1879068</v>
+        <v>1122739</v>
       </c>
       <c r="E27" s="106">
         <f>SUM(E23:E26)</f>
-        <v>1727051.3987999998</v>
+        <v>1031909.4148999999</v>
       </c>
       <c r="F27" s="106">
         <f>SUM(F23:F26)</f>
-        <v>152016.60119999998</v>
+        <v>90829.585100000011</v>
       </c>
       <c r="G27" s="107">
         <f>E27+F27</f>
-        <v>1879067.9999999998</v>
+        <v>1122738.9999999998</v>
       </c>
       <c r="H27" s="142" t="str">
         <f>IF(D27=G27, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="93" t="s">
         <v>109</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="194">
+      <c r="D28" s="193">
         <v>0</v>
       </c>
       <c r="E28" s="129">
@@ -2410,11 +2457,11 @@
       </c>
       <c r="H28" s="142"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="93"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="193">
+      <c r="D29" s="192">
         <v>0</v>
       </c>
       <c r="E29" s="129">
@@ -2427,25 +2474,25 @@
       </c>
       <c r="H29" s="142"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="93"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="193"/>
+      <c r="D30" s="192"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="H30" s="142"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="93"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="193"/>
+      <c r="D31" s="192"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="H31" s="142"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="94" t="s">
         <v>117</v>
       </c>
@@ -2472,13 +2519,13 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="93" t="s">
         <v>109</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="194"/>
+      <c r="D33" s="193"/>
       <c r="E33" s="129">
         <f>D33*91.91%</f>
         <v>0</v>
@@ -2489,13 +2536,13 @@
       </c>
       <c r="H33" s="142"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>130</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="193"/>
+      <c r="D34" s="192"/>
       <c r="E34" s="129">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
@@ -2506,13 +2553,13 @@
       </c>
       <c r="H34" s="142"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="93" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="193"/>
+      <c r="D35" s="192"/>
       <c r="E35" s="129">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -2523,7 +2570,7 @@
       </c>
       <c r="H35" s="142"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="94" t="s">
         <v>110</v>
       </c>
@@ -2543,34 +2590,34 @@
       </c>
       <c r="H36" s="142"/>
     </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="124"/>
       <c r="B37" s="97"/>
       <c r="C37" s="97"/>
-      <c r="D37" s="193"/>
+      <c r="D37" s="192"/>
       <c r="E37" s="118"/>
       <c r="F37" s="118"/>
       <c r="H37" s="142"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="124"/>
       <c r="B38" s="97"/>
       <c r="C38" s="97"/>
-      <c r="D38" s="193"/>
+      <c r="D38" s="192"/>
       <c r="E38" s="118"/>
       <c r="F38" s="118"/>
       <c r="H38" s="142"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="97"/>
       <c r="B39" s="97"/>
       <c r="C39" s="109"/>
-      <c r="D39" s="193"/>
+      <c r="D39" s="192"/>
       <c r="E39" s="118"/>
       <c r="F39" s="118"/>
       <c r="H39" s="142"/>
     </row>
-    <row r="40" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="94" t="s">
         <v>117</v>
       </c>
@@ -2587,50 +2634,41 @@
       </c>
       <c r="H40" s="142"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="93" t="s">
-        <v>161</v>
-      </c>
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="93"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="111">
-        <f>100000+12000+180000+105869</f>
-        <v>397869</v>
-      </c>
+      <c r="D41" s="111"/>
       <c r="E41" s="129">
         <f>D41*91.91%</f>
-        <v>365681.39789999998</v>
+        <v>0</v>
       </c>
       <c r="F41" s="129">
         <f>D41*8.09%</f>
-        <v>32187.6021</v>
+        <v>0</v>
       </c>
       <c r="H41" s="142"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="93" t="s">
-        <v>168</v>
-      </c>
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="93"/>
       <c r="B42" s="7"/>
       <c r="C42" s="97"/>
-      <c r="D42" s="111">
-        <v>4519.75</v>
-      </c>
+      <c r="D42" s="111"/>
       <c r="E42" s="129">
         <f>D42*91.91%</f>
-        <v>4154.1022249999996</v>
+        <v>0</v>
       </c>
       <c r="F42" s="129">
         <f>D42*8.09%</f>
-        <v>365.64777500000002</v>
+        <v>0</v>
       </c>
       <c r="H42" s="142"/>
     </row>
-    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="93"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="195"/>
+      <c r="D43" s="194"/>
       <c r="E43" s="129">
         <f>D43*91.91%</f>
         <v>0</v>
@@ -2641,7 +2679,7 @@
       </c>
       <c r="H43" s="142"/>
     </row>
-    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="94" t="s">
         <v>127</v>
       </c>
@@ -2649,36 +2687,36 @@
       <c r="C44" s="94"/>
       <c r="D44" s="106">
         <f>SUM(D41:D43)</f>
-        <v>402388.75</v>
+        <v>0</v>
       </c>
       <c r="E44" s="146">
         <f>SUM(E41:E43)</f>
-        <v>369835.50012499996</v>
+        <v>0</v>
       </c>
       <c r="F44" s="153">
         <f>SUM(F41:F43)</f>
-        <v>32553.249875000001</v>
+        <v>0</v>
       </c>
       <c r="G44" s="107">
         <f>E44+F44</f>
-        <v>402388.74999999994</v>
+        <v>0</v>
       </c>
       <c r="H44" s="142"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="93" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="195"/>
+      <c r="D45" s="194"/>
       <c r="E45" s="112"/>
       <c r="F45" s="99"/>
       <c r="H45" s="142"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="93" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="97"/>
@@ -2695,15 +2733,15 @@
       </c>
       <c r="H46" s="142"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="93" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="260">
+      <c r="D47" s="111">
         <f>198148.58+12006.81+108061.32</f>
         <v>318216.70999999996</v>
       </c>
@@ -2717,15 +2755,15 @@
       </c>
       <c r="H47" s="142"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="93" t="s">
         <v>135</v>
       </c>
       <c r="B48" s="97" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="260">
+      <c r="D48" s="111">
         <v>1064942.8600000001</v>
       </c>
       <c r="E48" s="129">
@@ -2738,7 +2776,7 @@
       </c>
       <c r="H48" s="142"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="94" t="s">
         <v>6</v>
       </c>
@@ -2765,24 +2803,24 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="195"/>
+      <c r="D50" s="194"/>
       <c r="E50" s="113"/>
       <c r="F50" s="7"/>
       <c r="H50" s="142"/>
     </row>
-    <row r="51" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="166" t="s">
         <v>137</v>
       </c>
       <c r="B51" s="158"/>
       <c r="C51" s="159"/>
-      <c r="D51" s="260">
+      <c r="D51" s="111">
         <v>434000</v>
       </c>
       <c r="E51" s="141">
@@ -2804,215 +2842,204 @@
       </c>
       <c r="J51" s="160"/>
     </row>
-    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="166" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B52" s="158"/>
       <c r="C52" s="159"/>
-      <c r="D52" s="260">
-        <v>16000</v>
+      <c r="D52" s="111">
+        <v>590000</v>
       </c>
       <c r="E52" s="141">
         <f>D52</f>
-        <v>16000</v>
+        <v>590000</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="107">
         <f>D52</f>
-        <v>16000</v>
+        <v>590000</v>
       </c>
       <c r="H52" s="148">
         <f>E52+F52</f>
-        <v>16000</v>
+        <v>590000</v>
       </c>
       <c r="I52" s="160"/>
       <c r="J52" s="160"/>
     </row>
-    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="119" t="s">
-        <v>8</v>
-      </c>
-      <c r="B53" s="149"/>
-      <c r="C53" s="7"/>
+    <row r="53" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="166" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="158"/>
+      <c r="C53" s="159"/>
       <c r="D53" s="111">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="E53" s="141">
-        <f t="shared" ref="E53:E58" si="7">D53*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F53" s="129">
-        <f t="shared" ref="F53:F58" si="8">D53*8.09%</f>
-        <v>0</v>
-      </c>
+        <f>D53</f>
+        <v>16000</v>
+      </c>
+      <c r="F53" s="7"/>
       <c r="G53" s="107">
-        <f t="shared" ref="G53:G65" si="9">D53</f>
-        <v>0</v>
+        <f>D53</f>
+        <v>16000</v>
       </c>
       <c r="H53" s="148">
-        <f t="shared" ref="H53:H65" si="10">E53+F53</f>
-        <v>0</v>
+        <f>E53+F53</f>
+        <v>16000</v>
       </c>
       <c r="I53" s="160"/>
       <c r="J53" s="160"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="93" t="s">
-        <v>152</v>
-      </c>
-      <c r="B54" s="7"/>
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="119" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="149"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="260">
-        <v>175450</v>
+      <c r="D54" s="111">
+        <v>195254</v>
       </c>
       <c r="E54" s="141">
-        <f t="shared" si="7"/>
-        <v>161256.09499999997</v>
+        <f t="shared" ref="E54:E61" si="7">D54*91.91%</f>
+        <v>179457.95139999999</v>
       </c>
       <c r="F54" s="129">
-        <f t="shared" si="8"/>
-        <v>14193.905000000001</v>
+        <f t="shared" ref="F54:F61" si="8">D54*8.09%</f>
+        <v>15796.0486</v>
       </c>
       <c r="G54" s="107">
-        <f t="shared" si="9"/>
-        <v>175450</v>
+        <f t="shared" ref="G54:G71" si="9">D54</f>
+        <v>195254</v>
       </c>
       <c r="H54" s="148">
-        <f t="shared" si="10"/>
-        <v>175449.99999999997</v>
-      </c>
-      <c r="I54" s="160">
-        <f t="shared" ref="I54:I64" si="11">H54-D54</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="160">
-        <f t="shared" ref="J54:J64" si="12">G54-D54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" ref="H54:H71" si="10">E54+F54</f>
+        <v>195254</v>
+      </c>
+      <c r="I54" s="160"/>
+      <c r="J54" s="160"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="93" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>155</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="111">
-        <v>129320</v>
+        <v>176418</v>
       </c>
       <c r="E55" s="141">
-        <f>D55*91.91%</f>
-        <v>118858.01199999999</v>
+        <f t="shared" si="7"/>
+        <v>162145.78379999998</v>
       </c>
       <c r="F55" s="129">
         <f t="shared" si="8"/>
-        <v>10461.987999999999</v>
+        <v>14272.216200000001</v>
       </c>
       <c r="G55" s="107">
         <f t="shared" si="9"/>
-        <v>129320</v>
+        <v>176418</v>
       </c>
       <c r="H55" s="148">
-        <f>E55+F55</f>
-        <v>129319.99999999999</v>
+        <f t="shared" si="10"/>
+        <v>176417.99999999997</v>
       </c>
       <c r="I55" s="160">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="I55:I70" si="11">H55-D55</f>
         <v>0</v>
       </c>
       <c r="J55" s="160">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" ref="J55:J70" si="12">G55-D55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="97" t="s">
-        <v>156</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="111">
-        <v>632643.17000000004</v>
+        <v>176418</v>
       </c>
       <c r="E56" s="141">
         <f t="shared" si="7"/>
-        <v>581462.33754700003</v>
+        <v>162145.78379999998</v>
       </c>
       <c r="F56" s="129">
         <f t="shared" si="8"/>
-        <v>51180.832453000003</v>
+        <v>14272.216200000001</v>
       </c>
       <c r="G56" s="107">
         <f t="shared" si="9"/>
-        <v>632643.17000000004</v>
+        <v>176418</v>
       </c>
       <c r="H56" s="148">
         <f t="shared" si="10"/>
-        <v>632643.17000000004</v>
-      </c>
-      <c r="I56" s="160">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="160">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+        <v>176417.99999999997</v>
+      </c>
+      <c r="I56" s="160"/>
+      <c r="J56" s="160"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="97" t="s">
-        <v>158</v>
+        <v>9</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="C57" s="7"/>
       <c r="D57" s="111">
-        <v>632643.17000000004</v>
+        <v>129320</v>
       </c>
       <c r="E57" s="141">
-        <f t="shared" si="7"/>
-        <v>581462.33754700003</v>
+        <f>D57*91.91%</f>
+        <v>118858.01199999999</v>
       </c>
       <c r="F57" s="129">
         <f t="shared" si="8"/>
-        <v>51180.832453000003</v>
-      </c>
-      <c r="G57" s="107"/>
-      <c r="H57" s="148"/>
-      <c r="I57" s="160"/>
-      <c r="J57" s="160"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="124" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="97" t="s">
-        <v>160</v>
-      </c>
-      <c r="C58" s="97"/>
-      <c r="D58" s="111">
-        <v>1080005.93</v>
-      </c>
+        <v>10461.987999999999</v>
+      </c>
+      <c r="G57" s="107">
+        <f t="shared" si="9"/>
+        <v>129320</v>
+      </c>
+      <c r="H57" s="148">
+        <f>E57+F57</f>
+        <v>129319.99999999999</v>
+      </c>
+      <c r="I57" s="160">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="160">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="97"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="111"/>
       <c r="E58" s="141">
         <f t="shared" si="7"/>
-        <v>992633.45026299986</v>
+        <v>0</v>
       </c>
       <c r="F58" s="129">
         <f t="shared" si="8"/>
-        <v>87372.479737000001</v>
+        <v>0</v>
       </c>
       <c r="G58" s="107">
         <f t="shared" si="9"/>
-        <v>1080005.93</v>
+        <v>0</v>
       </c>
       <c r="H58" s="148">
         <f t="shared" si="10"/>
-        <v>1080005.93</v>
+        <v>0</v>
       </c>
       <c r="I58" s="160">
         <f t="shared" si="11"/>
@@ -3023,27 +3050,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="217" t="s">
-        <v>159</v>
-      </c>
-      <c r="B59" s="218"/>
-      <c r="C59" s="219"/>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="124" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" s="97" t="s">
+        <v>153</v>
+      </c>
+      <c r="C59" s="97"/>
       <c r="D59" s="111">
-        <v>53400</v>
+        <v>1100467.26</v>
       </c>
       <c r="E59" s="141">
-        <f t="shared" ref="E59:E60" si="13">D59</f>
-        <v>53400</v>
-      </c>
-      <c r="F59" s="129"/>
+        <f t="shared" si="7"/>
+        <v>1011439.4586659999</v>
+      </c>
+      <c r="F59" s="129">
+        <f t="shared" si="8"/>
+        <v>89027.801334000003</v>
+      </c>
       <c r="G59" s="107">
         <f t="shared" si="9"/>
-        <v>53400</v>
+        <v>1100467.26</v>
       </c>
       <c r="H59" s="148">
         <f t="shared" si="10"/>
-        <v>53400</v>
+        <v>1100467.26</v>
       </c>
       <c r="I59" s="160">
         <f t="shared" si="11"/>
@@ -3054,27 +3086,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="192" t="s">
-        <v>164</v>
-      </c>
-      <c r="B60" s="190"/>
-      <c r="C60" s="191"/>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="221" t="s">
+        <v>163</v>
+      </c>
+      <c r="B60" s="222"/>
+      <c r="C60" s="223"/>
       <c r="D60" s="111">
-        <v>180000</v>
+        <v>55000</v>
       </c>
       <c r="E60" s="141">
-        <f t="shared" si="13"/>
-        <v>180000</v>
+        <f t="shared" ref="E60:E62" si="13">D60</f>
+        <v>55000</v>
       </c>
       <c r="F60" s="129"/>
       <c r="G60" s="107">
         <f t="shared" si="9"/>
-        <v>180000</v>
+        <v>55000</v>
       </c>
       <c r="H60" s="148">
         <f t="shared" si="10"/>
-        <v>180000</v>
+        <v>55000</v>
       </c>
       <c r="I60" s="160">
         <f t="shared" si="11"/>
@@ -3085,854 +3117,1030 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="189" t="s">
-        <v>162</v>
-      </c>
-      <c r="B61" s="97"/>
-      <c r="C61" s="97"/>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="201" t="s">
+        <v>173</v>
+      </c>
+      <c r="B61" s="190"/>
+      <c r="C61" s="191"/>
       <c r="D61" s="111">
-        <v>90000</v>
+        <v>60000</v>
       </c>
       <c r="E61" s="141">
-        <f t="shared" ref="E61:E64" si="14">D61</f>
-        <v>90000</v>
-      </c>
-      <c r="F61" s="129"/>
+        <f t="shared" si="7"/>
+        <v>55145.999999999993</v>
+      </c>
+      <c r="F61" s="129">
+        <f t="shared" si="8"/>
+        <v>4854</v>
+      </c>
       <c r="G61" s="107">
         <f t="shared" si="9"/>
-        <v>90000</v>
+        <v>60000</v>
       </c>
       <c r="H61" s="148">
         <f t="shared" si="10"/>
-        <v>90000</v>
-      </c>
-      <c r="I61" s="160"/>
-      <c r="J61" s="160"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="124" t="s">
-        <v>163</v>
+        <v>59999.999999999993</v>
+      </c>
+      <c r="I61" s="160">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="160">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="189" t="s">
+        <v>165</v>
       </c>
       <c r="B62" s="97"/>
       <c r="C62" s="97"/>
       <c r="D62" s="111">
-        <f>105869</f>
-        <v>105869</v>
+        <v>120000</v>
       </c>
       <c r="E62" s="141">
-        <f t="shared" ref="E62" si="15">D62*91.91%</f>
-        <v>97304.197899999985</v>
-      </c>
-      <c r="F62" s="129">
-        <f t="shared" ref="F62" si="16">D62*8.09%</f>
-        <v>8564.8021000000008</v>
-      </c>
+        <f t="shared" si="13"/>
+        <v>120000</v>
+      </c>
+      <c r="F62" s="129"/>
       <c r="G62" s="107">
-        <f t="shared" si="9"/>
-        <v>105869</v>
-      </c>
-      <c r="H62" s="148"/>
+        <f t="shared" ref="G62" si="14">D62</f>
+        <v>120000</v>
+      </c>
+      <c r="H62" s="148">
+        <f t="shared" ref="H62" si="15">E62+F62</f>
+        <v>120000</v>
+      </c>
       <c r="I62" s="160"/>
       <c r="J62" s="160"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="97" t="s">
-        <v>163</v>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="189" t="s">
+        <v>164</v>
       </c>
       <c r="B63" s="97"/>
       <c r="C63" s="97"/>
       <c r="D63" s="111">
-        <v>64963</v>
+        <v>37800</v>
       </c>
       <c r="E63" s="141">
-        <f t="shared" si="14"/>
-        <v>64963</v>
+        <f t="shared" ref="E63:E70" si="16">D63</f>
+        <v>37800</v>
       </c>
       <c r="F63" s="129"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="148"/>
+      <c r="G63" s="107">
+        <f t="shared" si="9"/>
+        <v>37800</v>
+      </c>
+      <c r="H63" s="148">
+        <f t="shared" si="10"/>
+        <v>37800</v>
+      </c>
       <c r="I63" s="160"/>
       <c r="J63" s="160"/>
     </row>
-    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
+    <row r="64" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="229" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64" s="230"/>
+      <c r="C64" s="231"/>
       <c r="D64" s="111">
-        <v>90325</v>
+        <v>450000</v>
       </c>
       <c r="E64" s="141">
-        <f t="shared" si="14"/>
-        <v>90325</v>
+        <f t="shared" ref="E64" si="17">D64</f>
+        <v>450000</v>
       </c>
       <c r="F64" s="129"/>
       <c r="G64" s="107">
-        <f t="shared" si="9"/>
-        <v>90325</v>
+        <f t="shared" ref="G64:G66" si="18">D64</f>
+        <v>450000</v>
       </c>
       <c r="H64" s="148">
-        <f t="shared" si="10"/>
-        <v>90325</v>
-      </c>
-      <c r="I64" s="160">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="160">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="223" t="s">
-        <v>157</v>
-      </c>
-      <c r="B65" s="224"/>
-      <c r="C65" s="225"/>
+        <f t="shared" ref="H64:H66" si="19">E64+F64</f>
+        <v>450000</v>
+      </c>
+      <c r="I64" s="160"/>
+      <c r="J64" s="160"/>
+    </row>
+    <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="235" t="s">
+        <v>172</v>
+      </c>
+      <c r="B65" s="236"/>
+      <c r="C65" s="237"/>
       <c r="D65" s="111">
-        <v>1056623.9099999999</v>
+        <v>120000</v>
       </c>
       <c r="E65" s="141">
-        <f t="shared" ref="E65" si="17">D65*91.91%</f>
-        <v>971143.03568099986</v>
+        <f t="shared" ref="E65:E66" si="20">D65*91.91%</f>
+        <v>110291.99999999999</v>
       </c>
       <c r="F65" s="129">
-        <f t="shared" ref="F65" si="18">D65*8.09%</f>
-        <v>85480.874318999995</v>
+        <f t="shared" ref="F65:F66" si="21">D65*8.09%</f>
+        <v>9708</v>
       </c>
       <c r="G65" s="107">
-        <f t="shared" si="9"/>
-        <v>1056623.9099999999</v>
+        <f t="shared" si="18"/>
+        <v>120000</v>
       </c>
       <c r="H65" s="148">
-        <f t="shared" si="10"/>
-        <v>1056623.9099999999</v>
+        <f t="shared" si="19"/>
+        <v>119999.99999999999</v>
       </c>
       <c r="I65" s="160"/>
       <c r="J65" s="160"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A66" s="94" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="273" t="s">
+        <v>174</v>
+      </c>
+      <c r="B66" s="199"/>
+      <c r="C66" s="200"/>
+      <c r="D66" s="111">
+        <v>150440.91</v>
+      </c>
+      <c r="E66" s="141">
+        <f t="shared" si="20"/>
+        <v>138270.24038099998</v>
+      </c>
+      <c r="F66" s="129">
+        <f t="shared" si="21"/>
+        <v>12170.669619</v>
+      </c>
+      <c r="G66" s="107">
+        <f t="shared" si="18"/>
+        <v>150440.91</v>
+      </c>
+      <c r="H66" s="148">
+        <f t="shared" si="19"/>
+        <v>150440.90999999997</v>
+      </c>
+      <c r="I66" s="160"/>
+      <c r="J66" s="160"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="273" t="s">
+        <v>175</v>
+      </c>
+      <c r="B67" s="199"/>
+      <c r="C67" s="200"/>
+      <c r="D67" s="111">
+        <v>145498.9</v>
+      </c>
+      <c r="E67" s="141">
+        <f t="shared" ref="E67:E68" si="22">D67*91.91%</f>
+        <v>133728.03898999997</v>
+      </c>
+      <c r="F67" s="129">
+        <f t="shared" ref="F67:F68" si="23">D67*8.09%</f>
+        <v>11770.861009999999</v>
+      </c>
+      <c r="G67" s="107">
+        <f t="shared" ref="G67:G68" si="24">D67</f>
+        <v>145498.9</v>
+      </c>
+      <c r="H67" s="148">
+        <f t="shared" ref="H67:H68" si="25">E67+F67</f>
+        <v>145498.89999999997</v>
+      </c>
+      <c r="I67" s="160"/>
+      <c r="J67" s="160"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="273" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" s="199"/>
+      <c r="C68" s="200"/>
+      <c r="D68" s="111">
+        <v>149999.93</v>
+      </c>
+      <c r="E68" s="141">
+        <f t="shared" si="22"/>
+        <v>137864.93566299998</v>
+      </c>
+      <c r="F68" s="129">
+        <f t="shared" si="23"/>
+        <v>12134.994337</v>
+      </c>
+      <c r="G68" s="107">
+        <f t="shared" si="24"/>
+        <v>149999.93</v>
+      </c>
+      <c r="H68" s="148">
+        <f t="shared" si="25"/>
+        <v>149999.93</v>
+      </c>
+      <c r="I68" s="160"/>
+      <c r="J68" s="160"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="273" t="s">
+        <v>176</v>
+      </c>
+      <c r="B69" s="199"/>
+      <c r="C69" s="200"/>
+      <c r="D69" s="111">
+        <v>149999.93</v>
+      </c>
+      <c r="E69" s="141">
+        <f t="shared" ref="E69" si="26">D69*91.91%</f>
+        <v>137864.93566299998</v>
+      </c>
+      <c r="F69" s="129">
+        <f t="shared" ref="F69" si="27">D69*8.09%</f>
+        <v>12134.994337</v>
+      </c>
+      <c r="G69" s="107">
+        <f t="shared" ref="G69" si="28">D69</f>
+        <v>149999.93</v>
+      </c>
+      <c r="H69" s="148">
+        <f t="shared" ref="H69" si="29">E69+F69</f>
+        <v>149999.93</v>
+      </c>
+      <c r="I69" s="160"/>
+      <c r="J69" s="160"/>
+    </row>
+    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="111">
+        <v>95175</v>
+      </c>
+      <c r="E70" s="141">
+        <f t="shared" si="16"/>
+        <v>95175</v>
+      </c>
+      <c r="F70" s="129"/>
+      <c r="G70" s="107">
+        <f t="shared" si="9"/>
+        <v>95175</v>
+      </c>
+      <c r="H70" s="148">
+        <f t="shared" si="10"/>
+        <v>95175</v>
+      </c>
+      <c r="I70" s="160">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="160">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="272"/>
+      <c r="B71" s="227"/>
+      <c r="C71" s="228"/>
+      <c r="D71" s="111"/>
+      <c r="E71" s="141"/>
+      <c r="F71" s="129"/>
+      <c r="G71" s="107">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="148">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I71" s="160"/>
+      <c r="J71" s="160"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="95"/>
-      <c r="C66" s="95"/>
-      <c r="D66" s="106">
-        <f>SUM(D51:D65)</f>
-        <v>4741243.18</v>
-      </c>
-      <c r="E66" s="106">
-        <f>SUM(E51:E65)</f>
-        <v>4432807.465938</v>
-      </c>
-      <c r="F66" s="106">
-        <f>SUM(F51:F65)</f>
-        <v>308435.71406200004</v>
-      </c>
-      <c r="G66" s="107">
-        <f>E66+F66</f>
-        <v>4741243.18</v>
-      </c>
-      <c r="H66" s="142" t="str">
-        <f>IF(D66=G66, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I66" s="160">
-        <f>D66-G66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="195"/>
-      <c r="E67" s="113"/>
-      <c r="F67" s="7"/>
-      <c r="H67" s="142"/>
-    </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="195"/>
-      <c r="E68" s="112"/>
-      <c r="F68" s="7"/>
-      <c r="H68" s="142"/>
-    </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="195"/>
-      <c r="E69" s="112"/>
-      <c r="F69" s="7"/>
-      <c r="H69" s="142"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="93" t="s">
-        <v>140</v>
-      </c>
-      <c r="B70" s="97"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="260">
-        <v>230700</v>
-      </c>
-      <c r="E70" s="141">
-        <f>D70*91.91%</f>
-        <v>212036.37</v>
-      </c>
-      <c r="F70" s="129">
-        <f>D70*8.09%</f>
-        <v>18663.63</v>
-      </c>
-      <c r="G70" s="147"/>
-      <c r="H70" s="142"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="124" t="s">
-        <v>165</v>
-      </c>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="111">
-        <v>30097.79</v>
-      </c>
-      <c r="E71" s="141">
-        <f>D71*91.91%</f>
-        <v>27662.878788999999</v>
-      </c>
-      <c r="F71" s="129">
-        <f>D71*8.09%</f>
-        <v>2434.9112110000001</v>
-      </c>
-      <c r="H71" s="142"/>
-      <c r="I71" s="107"/>
-    </row>
-    <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="94" t="s">
-        <v>16</v>
-      </c>
-      <c r="B72" s="94"/>
-      <c r="C72" s="94"/>
+      <c r="B72" s="95"/>
+      <c r="C72" s="95"/>
       <c r="D72" s="106">
-        <f>SUM(D70:D71)</f>
-        <v>260797.79</v>
+        <f>SUM(D51:D71)</f>
+        <v>4351791.93</v>
       </c>
       <c r="E72" s="106">
-        <f>SUM(E70:E71)</f>
-        <v>239699.248789</v>
+        <f>SUM(E51:E71)</f>
+        <v>4145188.1403629994</v>
       </c>
       <c r="F72" s="106">
-        <f>SUM(F70:F71)</f>
-        <v>21098.541211</v>
+        <f>SUM(F51:F71)</f>
+        <v>206603.78963700001</v>
       </c>
       <c r="G72" s="107">
         <f>E72+F72</f>
-        <v>260797.79</v>
+        <v>4351791.93</v>
       </c>
       <c r="H72" s="142" t="str">
         <f>IF(D72=G72, "", "Error")</f>
         <v/>
       </c>
-      <c r="J72" s="107"/>
-    </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I72" s="160">
+        <f>D72-G72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="195"/>
+      <c r="D73" s="194"/>
       <c r="E73" s="113"/>
       <c r="F73" s="7"/>
       <c r="H73" s="142"/>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
-      <c r="D74" s="195"/>
+      <c r="D74" s="194"/>
       <c r="E74" s="112"/>
       <c r="F74" s="7"/>
       <c r="H74" s="142"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="93" t="s">
-        <v>13</v>
-      </c>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
-      <c r="D75" s="195"/>
+      <c r="D75" s="194"/>
       <c r="E75" s="112"/>
       <c r="F75" s="7"/>
       <c r="H75" s="142"/>
     </row>
-    <row r="76" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="93" t="s">
-        <v>14</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>116</v>
-      </c>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="124" t="s">
+        <v>139</v>
+      </c>
+      <c r="B76" s="97"/>
       <c r="C76" s="7"/>
       <c r="D76" s="111">
-        <v>246000</v>
+        <v>230700</v>
       </c>
       <c r="E76" s="141">
         <f>D76*91.91%</f>
-        <v>226098.59999999998</v>
+        <v>212036.37</v>
       </c>
       <c r="F76" s="129">
         <f>D76*8.09%</f>
-        <v>19901.400000000001</v>
-      </c>
-      <c r="G76" t="s">
-        <v>138</v>
-      </c>
+        <v>18663.63</v>
+      </c>
+      <c r="G76" s="147"/>
       <c r="H76" s="142"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
+    <row r="77" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="232" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" s="233"/>
+      <c r="C77" s="234"/>
       <c r="D77" s="111">
-        <v>35000</v>
+        <v>227600</v>
       </c>
       <c r="E77" s="141">
-        <f>D77*91.91%</f>
-        <v>32168.499999999996</v>
-      </c>
-      <c r="F77" s="129">
-        <f>D77*8.09%</f>
-        <v>2831.5</v>
-      </c>
+        <f t="shared" ref="E77" si="30">D77</f>
+        <v>227600</v>
+      </c>
+      <c r="F77" s="129"/>
       <c r="H77" s="142"/>
-      <c r="J77" s="111"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" s="7"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="195"/>
-      <c r="E78" s="114"/>
-      <c r="F78" s="7"/>
-      <c r="H78" s="142"/>
+      <c r="I77" s="107"/>
+    </row>
+    <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B78" s="94"/>
+      <c r="C78" s="94"/>
+      <c r="D78" s="106">
+        <f>SUM(D76:D77)</f>
+        <v>458300</v>
+      </c>
+      <c r="E78" s="106">
+        <f>SUM(E76:E77)</f>
+        <v>439636.37</v>
+      </c>
+      <c r="F78" s="106">
+        <f>SUM(F76:F77)</f>
+        <v>18663.63</v>
+      </c>
+      <c r="G78" s="107">
+        <f>E78+F78</f>
+        <v>458300</v>
+      </c>
+      <c r="H78" s="142" t="str">
+        <f>IF(D78=G78, "", "Error")</f>
+        <v/>
+      </c>
       <c r="J78" s="107"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" s="94" t="s">
-        <v>100</v>
-      </c>
-      <c r="B79" s="94"/>
-      <c r="C79" s="94"/>
-      <c r="D79" s="106">
-        <f>SUM(D76:D78)</f>
-        <v>281000</v>
-      </c>
-      <c r="E79" s="106">
-        <f>SUM(E76:E78)</f>
-        <v>258267.09999999998</v>
-      </c>
-      <c r="F79" s="106">
-        <f>SUM(F76:F78)</f>
-        <v>22732.9</v>
-      </c>
-      <c r="G79" s="107">
-        <f>E79+F79</f>
-        <v>281000</v>
-      </c>
-      <c r="H79" s="142" t="str">
-        <f>IF(D79=G79, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J79" s="107"/>
-    </row>
-    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="93" t="s">
-        <v>100</v>
-      </c>
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="194"/>
+      <c r="E79" s="113"/>
+      <c r="F79" s="7"/>
+      <c r="H79" s="142"/>
+    </row>
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
-      <c r="D80" s="111"/>
-      <c r="E80" s="115"/>
+      <c r="D80" s="194"/>
+      <c r="E80" s="112"/>
       <c r="F80" s="7"/>
       <c r="H80" s="142"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="93" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
-      <c r="D81" s="111">
-        <v>131525.10999999999</v>
-      </c>
-      <c r="E81" s="141">
-        <f>D81*91.91%</f>
-        <v>120884.72860099998</v>
-      </c>
-      <c r="F81" s="129">
-        <f>D81*8.09%</f>
-        <v>10640.381398999998</v>
-      </c>
+      <c r="D81" s="194"/>
+      <c r="E81" s="112"/>
+      <c r="F81" s="7"/>
       <c r="H81" s="142"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="B82" s="7"/>
-      <c r="C82" s="120"/>
+        <v>14</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" s="7"/>
       <c r="D82" s="111">
-        <v>57500</v>
+        <v>285700</v>
       </c>
       <c r="E82" s="141">
         <f>D82*91.91%</f>
-        <v>52848.249999999993</v>
+        <v>262586.87</v>
       </c>
       <c r="F82" s="129">
         <f>D82*8.09%</f>
-        <v>4651.75</v>
+        <v>23113.13</v>
+      </c>
+      <c r="G82" t="s">
+        <v>168</v>
       </c>
       <c r="H82" s="142"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" s="94"/>
-      <c r="C83" s="94"/>
-      <c r="D83" s="145">
-        <f>SUM(D81:D82)</f>
-        <v>189025.11</v>
-      </c>
-      <c r="E83" s="139">
-        <f t="shared" ref="E83:F83" si="19">SUM(E81:E82)</f>
-        <v>173732.97860099998</v>
-      </c>
-      <c r="F83" s="139">
-        <f t="shared" si="19"/>
-        <v>15292.131398999998</v>
-      </c>
-      <c r="G83" s="107">
-        <f>E83+F83</f>
-        <v>189025.11</v>
-      </c>
-      <c r="H83" s="142" t="str">
-        <f>IF(D83=G83, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="111">
+        <v>35000</v>
+      </c>
+      <c r="E83" s="141">
+        <f>D83*91.91%</f>
+        <v>32168.499999999996</v>
+      </c>
+      <c r="F83" s="129">
+        <f>D83*8.09%</f>
+        <v>2831.5</v>
+      </c>
+      <c r="H83" s="142"/>
+      <c r="J83" s="111"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
-      <c r="D84" s="163"/>
-      <c r="E84" s="11"/>
+      <c r="D84" s="194"/>
+      <c r="E84" s="114"/>
       <c r="F84" s="7"/>
       <c r="H84" s="142"/>
-    </row>
-    <row r="85" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="98" t="s">
-        <v>133</v>
-      </c>
-      <c r="B85" s="98"/>
-      <c r="C85" s="98"/>
-      <c r="D85" s="164"/>
-      <c r="E85" s="116">
-        <f>D85*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F85" s="131">
-        <f>D85*8.09%</f>
-        <v>0</v>
+      <c r="J84" s="107"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="94" t="s">
+        <v>100</v>
+      </c>
+      <c r="B85" s="94"/>
+      <c r="C85" s="94"/>
+      <c r="D85" s="106">
+        <f>SUM(D82:D84)</f>
+        <v>320700</v>
+      </c>
+      <c r="E85" s="106">
+        <f>SUM(E82:E84)</f>
+        <v>294755.37</v>
+      </c>
+      <c r="F85" s="106">
+        <f>SUM(F82:F84)</f>
+        <v>25944.63</v>
       </c>
       <c r="G85" s="107">
         <f>E85+F85</f>
-        <v>0</v>
+        <v>320700</v>
       </c>
       <c r="H85" s="142" t="str">
         <f>IF(D85=G85, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="86" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="1"/>
-      <c r="D86" s="162"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="144"/>
+      <c r="J85" s="107"/>
+    </row>
+    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="93" t="s">
+        <v>100</v>
+      </c>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="111"/>
+      <c r="E86" s="115"/>
+      <c r="F86" s="7"/>
       <c r="H86" s="142"/>
     </row>
-    <row r="87" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="4" t="s">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="93" t="s">
+        <v>101</v>
+      </c>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="111">
+        <v>163564.31</v>
+      </c>
+      <c r="E87" s="141">
+        <f>D87*91.91%</f>
+        <v>150331.95732099999</v>
+      </c>
+      <c r="F87" s="129">
+        <f>D87*8.09%</f>
+        <v>13232.352679</v>
+      </c>
+      <c r="H87" s="142"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="93" t="s">
+        <v>102</v>
+      </c>
+      <c r="B88" s="7"/>
+      <c r="C88" s="120"/>
+      <c r="D88" s="111">
+        <v>57500</v>
+      </c>
+      <c r="E88" s="141">
+        <f>D88*91.91%</f>
+        <v>52848.249999999993</v>
+      </c>
+      <c r="F88" s="129">
+        <f>D88*8.09%</f>
+        <v>4651.75</v>
+      </c>
+      <c r="H88" s="142"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" s="94"/>
+      <c r="C89" s="94"/>
+      <c r="D89" s="145">
+        <f>SUM(D87:D88)</f>
+        <v>221064.31</v>
+      </c>
+      <c r="E89" s="139">
+        <f t="shared" ref="E89:F89" si="31">SUM(E87:E88)</f>
+        <v>203180.20732099999</v>
+      </c>
+      <c r="F89" s="139">
+        <f t="shared" si="31"/>
+        <v>17884.102679</v>
+      </c>
+      <c r="G89" s="107">
+        <f>E89+F89</f>
+        <v>221064.31</v>
+      </c>
+      <c r="H89" s="142" t="str">
+        <f>IF(D89=G89, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="163"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="7"/>
+      <c r="H90" s="142"/>
+    </row>
+    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="98" t="s">
+        <v>133</v>
+      </c>
+      <c r="B91" s="98"/>
+      <c r="C91" s="98"/>
+      <c r="D91" s="164">
+        <f>8500000-7864396.81</f>
+        <v>635603.19000000041</v>
+      </c>
+      <c r="E91" s="116">
+        <f>D91*91.91%</f>
+        <v>584182.89192900027</v>
+      </c>
+      <c r="F91" s="131">
+        <f>D91*8.09%</f>
+        <v>51420.298071000034</v>
+      </c>
+      <c r="G91" s="107">
+        <f>E91+F91</f>
+        <v>635603.19000000029</v>
+      </c>
+      <c r="H91" s="142" t="str">
+        <f>IF(D91=G91, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="D92" s="162"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="144"/>
+      <c r="H92" s="142"/>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B87" s="59"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="165">
-        <f>SUM(D85+D83+D79+D72+D66+D49+D32+D27+D44)</f>
-        <v>9143324.4000000004</v>
-      </c>
-      <c r="E87" s="140">
-        <f>SUM(E85+E83+E79+E72+E66+E49+E32+E27+E44)</f>
-        <v>8478760.3152399994</v>
-      </c>
-      <c r="F87" s="140">
-        <f>SUM(F85+F83+F79+F72+F66+F49+F32+F27+F44)</f>
-        <v>664564.08476</v>
-      </c>
-      <c r="G87" s="107">
-        <f>E87+F87</f>
-        <v>9143324.3999999985</v>
-      </c>
-      <c r="H87" s="142" t="str">
-        <f>IF(D87=G87, "", "Error")</f>
+      <c r="B93" s="59"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="165">
+        <f>SUM(D91+D89+D85+D78+D72+D49+D32+D27+D44)</f>
+        <v>8500000</v>
+      </c>
+      <c r="E93" s="140">
+        <f>SUM(E91+E89+E85+E78+E72+E49+E32+E27+E44)</f>
+        <v>7976219.0174999991</v>
+      </c>
+      <c r="F93" s="140">
+        <f>SUM(F91+F89+F85+F78+F72+F49+F32+F27+F44)</f>
+        <v>523780.98250000004</v>
+      </c>
+      <c r="G93" s="107">
+        <f>E93+F93</f>
+        <v>8500000</v>
+      </c>
+      <c r="H93" s="142" t="str">
+        <f>IF(D93=G93, "", "Error")</f>
         <v/>
       </c>
-      <c r="I87" s="160">
-        <f>D87-G87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D88" s="162"/>
-      <c r="E88" s="107"/>
-    </row>
-    <row r="89" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="169" t="s">
-        <v>151</v>
-      </c>
-      <c r="B89" s="136"/>
-      <c r="C89" s="136"/>
-      <c r="E89" s="107"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A90" s="1"/>
-      <c r="C90" s="134"/>
-      <c r="E90" s="107"/>
-    </row>
-    <row r="91" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="1"/>
-      <c r="C91" s="134"/>
-      <c r="E91" s="107"/>
-    </row>
-    <row r="92" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="137" t="s">
+      <c r="I93" s="160">
+        <f>D93-G93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D94" s="162"/>
+      <c r="E94" s="107"/>
+    </row>
+    <row r="95" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="169" t="s">
+        <v>150</v>
+      </c>
+      <c r="B95" s="136"/>
+      <c r="C95" s="136"/>
+      <c r="E95" s="107"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="C96" s="134"/>
+      <c r="E96" s="107"/>
+    </row>
+    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1"/>
+      <c r="C97" s="134"/>
+      <c r="E97" s="107"/>
+    </row>
+    <row r="98" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="137" t="s">
         <v>29</v>
       </c>
-      <c r="B92" s="138"/>
-      <c r="C92" s="135">
-        <f>SUM(C90:C91)</f>
-        <v>0</v>
-      </c>
-      <c r="E92" s="107"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E93" s="107"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E94" s="132"/>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="215" t="s">
+      <c r="B98" s="138"/>
+      <c r="C98" s="135">
+        <f>SUM(C96:C97)</f>
+        <v>0</v>
+      </c>
+      <c r="E98" s="107"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E99" s="107"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E100" s="132"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="219" t="s">
         <v>113</v>
       </c>
-      <c r="B95" s="216"/>
-      <c r="C95" s="216"/>
-      <c r="D95" s="216"/>
-      <c r="E95" s="155" t="s">
+      <c r="B101" s="220"/>
+      <c r="C101" s="220"/>
+      <c r="D101" s="220"/>
+      <c r="E101" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="F95" s="156" t="s">
+      <c r="F101" s="156" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="212"/>
-      <c r="B96" s="213"/>
-      <c r="C96" s="214"/>
-      <c r="D96" s="111"/>
-      <c r="E96" s="141">
-        <f t="shared" ref="E96:E97" si="20">D96*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F96" s="129">
-        <f t="shared" ref="F96:F97" si="21">D96*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="220"/>
-      <c r="B97" s="221"/>
-      <c r="C97" s="222"/>
-      <c r="D97" s="111"/>
-      <c r="E97" s="141">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="F97" s="129">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A98" s="209" t="s">
+    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="216"/>
+      <c r="B102" s="217"/>
+      <c r="C102" s="218"/>
+      <c r="D102" s="111"/>
+      <c r="E102" s="141">
+        <f t="shared" ref="E102:E103" si="32">D102*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F102" s="129">
+        <f t="shared" ref="F102:F103" si="33">D102*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="224"/>
+      <c r="B103" s="225"/>
+      <c r="C103" s="226"/>
+      <c r="D103" s="111"/>
+      <c r="E103" s="141">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="129">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="213" t="s">
         <v>29</v>
       </c>
-      <c r="B98" s="210"/>
-      <c r="C98" s="211"/>
-      <c r="D98" s="154">
-        <f>SUM(D96:D97)</f>
-        <v>0</v>
-      </c>
-      <c r="E98" s="154">
-        <f>SUM(E96:E97)</f>
-        <v>0</v>
-      </c>
-      <c r="F98" s="154">
-        <f>SUM(F96:F97)</f>
-        <v>0</v>
-      </c>
-      <c r="H98" s="107">
-        <f>E98+F98</f>
-        <v>0</v>
-      </c>
-      <c r="I98" s="142" t="str">
-        <f>IF(D98=H98, "", "Error")</f>
+      <c r="B104" s="214"/>
+      <c r="C104" s="215"/>
+      <c r="D104" s="154">
+        <f>SUM(D102:D103)</f>
+        <v>0</v>
+      </c>
+      <c r="E104" s="154">
+        <f>SUM(E102:E103)</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="154">
+        <f>SUM(F102:F103)</f>
+        <v>0</v>
+      </c>
+      <c r="H104" s="107">
+        <f>E104+F104</f>
+        <v>0</v>
+      </c>
+      <c r="I104" s="142" t="str">
+        <f>IF(D104=H104, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E100" s="107"/>
-    </row>
-    <row r="101" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="101" t="s">
+    <row r="106" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E106" s="107"/>
+    </row>
+    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="101" t="s">
         <v>104</v>
       </c>
-      <c r="B101" s="102">
-        <f>D87</f>
-        <v>9143324.4000000004</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="103" t="s">
+      <c r="B107" s="102">
+        <f>D93</f>
+        <v>8500000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="103" t="s">
         <v>106</v>
       </c>
-      <c r="B102" s="104">
-        <f>D87-D85</f>
-        <v>9143324.4000000004</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D103" s="199"/>
-      <c r="E103" s="199"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" s="73" t="s">
+      <c r="B108" s="104">
+        <f>D93-D91</f>
+        <v>7864396.8099999996</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D109" s="203"/>
+      <c r="E109" s="203"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="B104" s="74"/>
-      <c r="C104" s="75"/>
-      <c r="D104" s="199"/>
-      <c r="E104" s="199"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="76" t="s">
+      <c r="B110" s="74"/>
+      <c r="C110" s="75"/>
+      <c r="D110" s="203"/>
+      <c r="E110" s="203"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="B105" s="10">
-        <v>2735299.703127617</v>
-      </c>
-      <c r="C105" s="77"/>
-      <c r="D105" s="199"/>
-      <c r="E105" s="199"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="78" t="s">
+      <c r="B111" s="10">
+        <v>2579766.3959282823</v>
+      </c>
+      <c r="C111" s="77"/>
+      <c r="D111" s="203"/>
+      <c r="E111" s="203"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="B106" s="91">
+      <c r="B112" s="91">
         <f>PRORRATEO!G52</f>
-        <v>8413417.1728006657</v>
-      </c>
-      <c r="C106" s="77" t="s">
+        <v>9493696.4535236657</v>
+      </c>
+      <c r="C112" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="D106" s="199"/>
-      <c r="E106" s="199"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="78" t="s">
+      <c r="D112" s="203"/>
+      <c r="E112" s="203"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="78" t="s">
         <v>115</v>
       </c>
-      <c r="B107" s="157">
-        <f>-B102</f>
-        <v>-9143324.4000000004</v>
-      </c>
-      <c r="C107" s="75"/>
-      <c r="D107" s="199"/>
-      <c r="E107" s="199"/>
-      <c r="G107" s="111"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="78" t="s">
+      <c r="B113" s="157">
+        <f>-B108</f>
+        <v>-7864396.8099999996</v>
+      </c>
+      <c r="C113" s="75"/>
+      <c r="D113" s="203"/>
+      <c r="E113" s="203"/>
+      <c r="G113" s="111"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="B108" s="157">
-        <f>-D98</f>
-        <v>0</v>
-      </c>
-      <c r="C108" s="75"/>
-      <c r="D108" s="199"/>
-      <c r="E108" s="199"/>
-      <c r="G108" s="121"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="78" t="s">
+      <c r="B114" s="157">
+        <f>-D104</f>
+        <v>0</v>
+      </c>
+      <c r="C114" s="75"/>
+      <c r="D114" s="203"/>
+      <c r="E114" s="203"/>
+      <c r="G114" s="121"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="B109" s="157">
-        <f>-B116</f>
-        <v>-10000</v>
-      </c>
-      <c r="C109" s="79"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="78" t="s">
+      <c r="B115" s="157">
+        <f>-B122</f>
+        <v>-20000</v>
+      </c>
+      <c r="C115" s="79"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="B110" s="92">
-        <f>-C92</f>
-        <v>0</v>
-      </c>
-      <c r="C110" s="79"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="78"/>
-      <c r="B111" s="74"/>
-      <c r="C111" s="143"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="76" t="s">
+      <c r="B116" s="92">
+        <f>-C98</f>
+        <v>0</v>
+      </c>
+      <c r="C116" s="79"/>
+    </row>
+    <row r="117" spans="1:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="198" t="s">
+        <v>166</v>
+      </c>
+      <c r="B117" s="197">
+        <v>-120000</v>
+      </c>
+      <c r="C117" s="143"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="B112" s="80">
-        <f>SUM(B105:B111)</f>
-        <v>1995392.4759282824</v>
-      </c>
-      <c r="C112" s="143"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A113" s="79"/>
-      <c r="C113" s="75"/>
-      <c r="D113" s="82"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C114" s="75"/>
-      <c r="D114" s="107"/>
-      <c r="E114" s="160"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A115" s="73" t="s">
+      <c r="B118" s="80">
+        <f>SUM(B111:B117)</f>
+        <v>4069066.0394519484</v>
+      </c>
+      <c r="C118" s="143"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="79"/>
+      <c r="C119" s="75"/>
+      <c r="D119" s="82"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C120" s="75"/>
+      <c r="D120" s="107"/>
+      <c r="E120" s="160"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="B115" s="174">
-        <v>-192694.54000000004</v>
-      </c>
-      <c r="C115" s="81"/>
-      <c r="D115" s="160"/>
-      <c r="E115" s="160"/>
-      <c r="F115" s="160"/>
-    </row>
-    <row r="116" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="76" t="s">
-        <v>172</v>
-      </c>
-      <c r="B116" s="92">
-        <v>10000</v>
-      </c>
-      <c r="C116" s="81"/>
-      <c r="D116" s="160"/>
-      <c r="E116" s="167"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A117" s="76"/>
-      <c r="B117" s="157"/>
-      <c r="C117" s="81"/>
-      <c r="E117" s="107"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A118" s="76"/>
-      <c r="B118" s="157"/>
-      <c r="C118" s="81"/>
-      <c r="E118" s="107"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A119" s="99" t="s">
+      <c r="B121" s="174">
+        <v>-182694.54000000004</v>
+      </c>
+      <c r="C121" s="81"/>
+      <c r="D121" s="160"/>
+      <c r="E121" s="160"/>
+      <c r="F121" s="160"/>
+    </row>
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="B122" s="92">
+        <v>20000</v>
+      </c>
+      <c r="C122" s="81"/>
+      <c r="D122" s="160"/>
+      <c r="E122" s="167"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="76"/>
+      <c r="B123" s="157"/>
+      <c r="C123" s="81"/>
+      <c r="E123" s="107"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="76"/>
+      <c r="B124" s="157"/>
+      <c r="C124" s="81"/>
+      <c r="E124" s="107"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="B119" s="100">
-        <f>SUM(B115:B118)</f>
-        <v>-182694.54000000004</v>
-      </c>
-      <c r="C119" s="81"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C120" s="82"/>
-      <c r="D120" s="160"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B121" s="79"/>
-      <c r="C121" s="75"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N123" s="11"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B126" s="198"/>
-      <c r="C126" s="198"/>
-      <c r="D126" s="198"/>
-      <c r="E126" s="198"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B127" s="198"/>
-      <c r="C127" s="198"/>
-      <c r="D127" s="198"/>
-      <c r="E127" s="198"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B128" s="198"/>
-      <c r="C128" s="198"/>
-      <c r="D128" s="198"/>
-      <c r="E128" s="198"/>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B129" s="198"/>
-      <c r="C129" s="198"/>
-      <c r="D129" s="198"/>
-      <c r="E129" s="198"/>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B130" s="198"/>
-      <c r="C130" s="198"/>
-      <c r="D130" s="198"/>
-      <c r="E130" s="198"/>
+      <c r="B125" s="100">
+        <f>SUM(B121:B124)</f>
+        <v>-162694.54000000004</v>
+      </c>
+      <c r="C125" s="81"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C126" s="82"/>
+      <c r="D126" s="160"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B127" s="79"/>
+      <c r="C127" s="75"/>
+    </row>
+    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N129" s="11"/>
+    </row>
+    <row r="132" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B132" s="202"/>
+      <c r="C132" s="202"/>
+      <c r="D132" s="202"/>
+      <c r="E132" s="202"/>
+    </row>
+    <row r="133" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B133" s="202"/>
+      <c r="C133" s="202"/>
+      <c r="D133" s="202"/>
+      <c r="E133" s="202"/>
+    </row>
+    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B134" s="202"/>
+      <c r="C134" s="202"/>
+      <c r="D134" s="202"/>
+      <c r="E134" s="202"/>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B135" s="202"/>
+      <c r="C135" s="202"/>
+      <c r="D135" s="202"/>
+      <c r="E135" s="202"/>
+    </row>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B136" s="202"/>
+      <c r="C136" s="202"/>
+      <c r="D136" s="202"/>
+      <c r="E136" s="202"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B126:E130"/>
-    <mergeCell ref="D103:E108"/>
+  <mergeCells count="12">
+    <mergeCell ref="B132:E136"/>
+    <mergeCell ref="D109:E114"/>
     <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A95:D95"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A77:C77"/>
     <mergeCell ref="A65:C65"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3944,64 +4152,62 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
-    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="240" t="s">
-        <v>153</v>
-      </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="241"/>
-      <c r="H1" s="241"/>
-      <c r="I1" s="241"/>
-      <c r="J1" s="242"/>
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="251"/>
+      <c r="B1" s="252"/>
+      <c r="C1" s="252"/>
+      <c r="D1" s="252"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="252"/>
+      <c r="G1" s="252"/>
+      <c r="H1" s="252"/>
+      <c r="I1" s="252"/>
+      <c r="J1" s="253"/>
       <c r="K1" s="178" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="229">
-        <f>RESUMEN!D87</f>
-        <v>9143324.4000000004</v>
-      </c>
-      <c r="M1" s="230"/>
+      <c r="L1" s="238">
+        <f>RESUMEN!D93</f>
+        <v>8500000</v>
+      </c>
+      <c r="M1" s="239"/>
       <c r="N1" s="179"/>
       <c r="O1" s="130">
         <f>L1*8.09%</f>
-        <v>739694.94396000006</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="243"/>
-      <c r="B2" s="244"/>
-      <c r="C2" s="244"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="244"/>
-      <c r="F2" s="244"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="244"/>
-      <c r="I2" s="244"/>
-      <c r="J2" s="245"/>
+        <v>687650</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="254"/>
+      <c r="B2" s="255"/>
+      <c r="C2" s="255"/>
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="255"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="256"/>
       <c r="K2" s="180" t="s">
         <v>125</v>
       </c>
@@ -4012,42 +4218,42 @@
       <c r="N2" s="182"/>
       <c r="O2" s="130">
         <f>O1-K7-553-50-86-8</f>
-        <v>115765.15710300021</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="243"/>
-      <c r="B3" s="244"/>
-      <c r="C3" s="244"/>
-      <c r="D3" s="244"/>
-      <c r="E3" s="244"/>
-      <c r="F3" s="244"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="244"/>
-      <c r="I3" s="244"/>
-      <c r="J3" s="245"/>
+        <v>63720.213143000146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="254"/>
+      <c r="B3" s="255"/>
+      <c r="C3" s="255"/>
+      <c r="D3" s="255"/>
+      <c r="E3" s="255"/>
+      <c r="F3" s="255"/>
+      <c r="G3" s="255"/>
+      <c r="H3" s="255"/>
+      <c r="I3" s="255"/>
+      <c r="J3" s="256"/>
       <c r="K3" s="180" t="s">
         <v>131</v>
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="183">
-        <f>RESUMEN!D98</f>
+        <f>RESUMEN!D104</f>
         <v>0</v>
       </c>
       <c r="N3" s="184"/>
       <c r="O3" s="72"/>
     </row>
-    <row r="4" spans="1:16" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="246"/>
-      <c r="B4" s="247"/>
-      <c r="C4" s="247"/>
-      <c r="D4" s="247"/>
-      <c r="E4" s="247"/>
-      <c r="F4" s="247"/>
-      <c r="G4" s="247"/>
-      <c r="H4" s="247"/>
-      <c r="I4" s="247"/>
-      <c r="J4" s="248"/>
+    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="257"/>
+      <c r="B4" s="258"/>
+      <c r="C4" s="258"/>
+      <c r="D4" s="258"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="258"/>
+      <c r="G4" s="258"/>
+      <c r="H4" s="258"/>
+      <c r="I4" s="258"/>
+      <c r="J4" s="259"/>
       <c r="K4" s="185" t="s">
         <v>125</v>
       </c>
@@ -4061,67 +4267,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="226" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="242" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="249" t="s">
+      <c r="B5" s="260" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="226" t="s">
+      <c r="C5" s="242" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="238" t="s">
+      <c r="D5" s="249" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="226" t="s">
+      <c r="E5" s="242" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="226" t="s">
+      <c r="F5" s="242" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="226" t="s">
+      <c r="G5" s="242" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="233" t="s">
+      <c r="H5" s="244" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="238" t="s">
+      <c r="I5" s="249" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="231" t="s">
+      <c r="J5" s="240" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="231" t="s">
+      <c r="K5" s="240" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="236" t="s">
+      <c r="L5" s="247" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="231" t="s">
+      <c r="M5" s="240" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="231" t="s">
+      <c r="N5" s="240" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="227"/>
-      <c r="B6" s="250"/>
-      <c r="C6" s="227"/>
-      <c r="D6" s="251"/>
-      <c r="E6" s="227"/>
-      <c r="F6" s="227"/>
-      <c r="G6" s="227"/>
-      <c r="H6" s="234"/>
-      <c r="I6" s="239"/>
-      <c r="J6" s="232"/>
-      <c r="K6" s="235"/>
-      <c r="L6" s="237"/>
-      <c r="M6" s="235"/>
-      <c r="N6" s="232"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="243"/>
+      <c r="B6" s="261"/>
+      <c r="C6" s="243"/>
+      <c r="D6" s="262"/>
+      <c r="E6" s="243"/>
+      <c r="F6" s="243"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="245"/>
+      <c r="I6" s="250"/>
+      <c r="J6" s="241"/>
+      <c r="K6" s="246"/>
+      <c r="L6" s="248"/>
+      <c r="M6" s="246"/>
+      <c r="N6" s="241"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
@@ -4136,11 +4342,11 @@
         <v>8.09</v>
       </c>
       <c r="F7" s="87">
-        <v>436413.50613400002</v>
-      </c>
-      <c r="G7" s="196">
+        <v>623232.78685699985</v>
+      </c>
+      <c r="G7" s="195">
         <f>F7</f>
-        <v>436413.50613400002</v>
+        <v>623232.78685699985</v>
       </c>
       <c r="H7" s="126">
         <f>F7-G7</f>
@@ -4165,7 +4371,7 @@
         <v>660626.7540684198</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
@@ -4180,17 +4386,17 @@
         <v>2.21</v>
       </c>
       <c r="F8" s="87">
-        <v>175332.93683118251</v>
-      </c>
-      <c r="G8" s="196">
-        <v>176000</v>
+        <v>208546.27016451585</v>
+      </c>
+      <c r="G8" s="195">
+        <v>209000</v>
       </c>
       <c r="H8" s="126">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>-667.0631688174908</v>
+        <v>-453.72983548414777</v>
       </c>
       <c r="I8" s="105">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J8" s="87">
         <f>M$4*E8%</f>
@@ -4203,14 +4409,14 @@
       <c r="L8" s="176"/>
       <c r="M8" s="6">
         <f>K8+J8+H8+L8</f>
-        <v>208546.27016451585</v>
+        <v>208759.6034978492</v>
       </c>
       <c r="N8" s="10">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>221059.04637438682</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>221285.17970772015</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
@@ -4225,18 +4431,18 @@
         <v>4.21</v>
       </c>
       <c r="F9" s="87">
-        <v>335396.60286759667</v>
-      </c>
-      <c r="G9" s="197">
-        <f>378417-G34</f>
-        <v>335397</v>
+        <v>398546.26953426335</v>
+      </c>
+      <c r="G9" s="196">
+        <f>449666-G34</f>
+        <v>398546</v>
       </c>
       <c r="H9" s="126">
         <f t="shared" si="0"/>
-        <v>-0.39713240333367139</v>
+        <v>0.26953426335239783</v>
       </c>
       <c r="I9" s="105">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J9" s="87">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
@@ -4249,14 +4455,14 @@
       <c r="L9" s="176"/>
       <c r="M9" s="6">
         <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>398546.26953426335</v>
+        <v>398546.93620093004</v>
       </c>
       <c r="N9" s="10">
         <f t="shared" si="1"/>
-        <v>422459.04570631916</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>422459.75237298582</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>38</v>
       </c>
@@ -4271,18 +4477,18 @@
         <v>2.84</v>
       </c>
       <c r="F10" s="87">
-        <v>226253.33333333334</v>
-      </c>
-      <c r="G10" s="196">
+        <v>268853.33333333331</v>
+      </c>
+      <c r="G10" s="195">
         <f>F10</f>
-        <v>226253.33333333334</v>
+        <v>268853.33333333331</v>
       </c>
       <c r="H10" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I10" s="105">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" s="87">
         <f t="shared" si="2"/>
@@ -4302,7 +4508,7 @@
         <v>284984.53333333333</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -4317,11 +4523,11 @@
         <v>3.43</v>
       </c>
       <c r="F11" s="87">
-        <v>273256.66666666669</v>
-      </c>
-      <c r="G11" s="196">
+        <v>324706.66666666669</v>
+      </c>
+      <c r="G11" s="195">
         <f>F11</f>
-        <v>273256.66666666669</v>
+        <v>324706.66666666669</v>
       </c>
       <c r="H11" s="126">
         <f t="shared" si="0"/>
@@ -4349,7 +4555,7 @@
       </c>
       <c r="P11" s="107"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -4364,18 +4570,18 @@
         <v>2.84</v>
       </c>
       <c r="F12" s="87">
-        <v>226253.33333333334</v>
-      </c>
-      <c r="G12" s="197">
+        <v>268853.33333333331</v>
+      </c>
+      <c r="G12" s="196">
         <f>F12</f>
-        <v>226253.33333333334</v>
+        <v>268853.33333333331</v>
       </c>
       <c r="H12" s="126">
         <f>F12-G12</f>
         <v>0</v>
       </c>
       <c r="I12" s="105">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="87">
         <f t="shared" si="2"/>
@@ -4395,7 +4601,7 @@
         <v>284984.53333333333</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -4410,18 +4616,18 @@
         <v>3.43</v>
       </c>
       <c r="F13" s="87">
-        <v>273256.48408590845</v>
-      </c>
-      <c r="G13" s="197">
-        <f>320260-G50</f>
-        <v>273256.66666666669</v>
+        <v>324706.48408590845</v>
+      </c>
+      <c r="G13" s="196">
+        <f>380559-G50</f>
+        <v>324705.66666666669</v>
       </c>
       <c r="H13" s="126">
         <f t="shared" si="0"/>
-        <v>-0.18258075823541731</v>
+        <v>0.81741924176458269</v>
       </c>
       <c r="I13" s="105">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="87">
         <f t="shared" si="2"/>
@@ -4434,14 +4640,14 @@
       <c r="L13" s="176"/>
       <c r="M13" s="6">
         <f t="shared" si="4"/>
-        <v>324706.48408590845</v>
+        <v>324707.48408590845</v>
       </c>
       <c r="N13" s="10">
         <f t="shared" si="1"/>
-        <v>344188.87313106295</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>344189.93313106295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
@@ -4456,17 +4662,18 @@
         <v>2.84</v>
       </c>
       <c r="F14" s="87">
-        <v>223995.45466666669</v>
-      </c>
-      <c r="G14" s="196">
-        <v>211300</v>
+        <v>298442</v>
+      </c>
+      <c r="G14" s="195">
+        <f>F14</f>
+        <v>298442</v>
       </c>
       <c r="H14" s="126">
         <f t="shared" si="0"/>
-        <v>12695.454666666687</v>
+        <v>0</v>
       </c>
       <c r="I14" s="105">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J14" s="87">
         <f t="shared" si="2"/>
@@ -4479,14 +4686,14 @@
       <c r="L14" s="176"/>
       <c r="M14" s="6">
         <f t="shared" si="4"/>
-        <v>281548.788</v>
+        <v>268853.33333333331</v>
       </c>
       <c r="N14" s="10">
         <f t="shared" si="1"/>
-        <v>298441.71528</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>284984.53333333333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>43</v>
       </c>
@@ -4495,25 +4702,20 @@
         <v>31</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E15" s="7">
         <v>3.43</v>
       </c>
       <c r="F15" s="87">
-        <v>273256.53766320064</v>
-      </c>
-      <c r="G15" s="197">
-        <f>313090-G35</f>
-        <v>273256.66666666669</v>
-      </c>
+        <v>324706.53766320064</v>
+      </c>
+      <c r="G15" s="196"/>
       <c r="H15" s="126">
         <f t="shared" si="0"/>
-        <v>-0.12900346604874358</v>
-      </c>
-      <c r="I15" s="105">
-        <v>9</v>
-      </c>
+        <v>324706.53766320064</v>
+      </c>
+      <c r="I15" s="105"/>
       <c r="J15" s="87">
         <f t="shared" si="2"/>
         <v>33156.666666666672</v>
@@ -4525,14 +4727,14 @@
       <c r="L15" s="176"/>
       <c r="M15" s="6">
         <f t="shared" si="4"/>
-        <v>324706.53766320064</v>
+        <v>649413.20432986738</v>
       </c>
       <c r="N15" s="10">
         <f t="shared" si="1"/>
-        <v>344188.92992299265</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>688377.99658965948</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -4547,18 +4749,18 @@
         <v>2.84</v>
       </c>
       <c r="F16" s="87">
-        <v>211229.0312833334</v>
-      </c>
-      <c r="G16" s="197">
-        <f>250266-G49</f>
-        <v>211229.33333333334</v>
+        <v>284984.2131603334</v>
+      </c>
+      <c r="G16" s="196">
+        <f>315240-G49</f>
+        <v>266070.13333333336</v>
       </c>
       <c r="H16" s="126">
         <f t="shared" si="0"/>
-        <v>-0.30204999994020909</v>
+        <v>18914.079827000038</v>
       </c>
       <c r="I16" s="105">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J16" s="87">
         <f t="shared" si="2"/>
@@ -4571,14 +4773,14 @@
       <c r="L16" s="176"/>
       <c r="M16" s="6">
         <f t="shared" si="4"/>
-        <v>268853.03128333337</v>
+        <v>287767.41316033335</v>
       </c>
       <c r="N16" s="10">
         <f t="shared" si="1"/>
-        <v>284984.2131603334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+        <v>305033.45794995333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
@@ -4593,18 +4795,18 @@
         <v>3.43</v>
       </c>
       <c r="F17" s="87">
-        <v>273256.30734444811</v>
-      </c>
-      <c r="G17" s="196">
-        <f>352126-G47-G48</f>
-        <v>273256</v>
+        <v>324706.9740111148</v>
+      </c>
+      <c r="G17" s="195">
+        <f>418427-G47-G48</f>
+        <v>324707</v>
       </c>
       <c r="H17" s="126">
         <f t="shared" si="0"/>
-        <v>0.30734444811241701</v>
+        <v>-2.5988885201513767E-2</v>
       </c>
       <c r="I17" s="105">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J17" s="87">
         <f t="shared" si="2"/>
@@ -4614,17 +4816,19 @@
         <f t="shared" si="3"/>
         <v>291550</v>
       </c>
-      <c r="L17" s="176"/>
+      <c r="L17" s="176">
+        <v>20000</v>
+      </c>
       <c r="M17" s="6">
         <f t="shared" si="4"/>
-        <v>324706.9740111148</v>
+        <v>344706.64067778148</v>
       </c>
       <c r="N17" s="10">
         <f t="shared" si="1"/>
-        <v>344189.39245178166</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+        <v>365389.03911844839</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -4633,24 +4837,24 @@
         <v>34</v>
       </c>
       <c r="D18" s="128" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="E18" s="7">
         <v>2.84</v>
       </c>
       <c r="F18" s="87">
-        <v>225086.09379991802</v>
-      </c>
-      <c r="G18" s="196">
-        <f>271000-G51</f>
-        <v>225590</v>
+        <v>268349.42713325133</v>
+      </c>
+      <c r="G18" s="195">
+        <f>322309-G51</f>
+        <v>268349</v>
       </c>
       <c r="H18" s="126">
         <f t="shared" si="0"/>
-        <v>-503.90620008198312</v>
+        <v>0.42713325133081526</v>
       </c>
       <c r="I18" s="105">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J18" s="87">
         <f t="shared" si="2"/>
@@ -4663,17 +4867,17 @@
       <c r="L18" s="176"/>
       <c r="M18" s="6">
         <f t="shared" si="4"/>
-        <v>268349.42713325133</v>
+        <v>268853.76046658464</v>
       </c>
       <c r="N18" s="10">
         <f t="shared" si="1"/>
-        <v>284450.39276124642</v>
+        <v>284984.98609457974</v>
       </c>
       <c r="P18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
@@ -4688,18 +4892,18 @@
         <v>3.43</v>
       </c>
       <c r="F19" s="87">
-        <v>273256.81964850141</v>
-      </c>
-      <c r="G19" s="197">
-        <f>316277-G41</f>
-        <v>273257</v>
+        <v>324706.48631516809</v>
+      </c>
+      <c r="G19" s="196">
+        <f>375826-G41</f>
+        <v>324706</v>
       </c>
       <c r="H19" s="126">
         <f t="shared" si="0"/>
-        <v>-0.18035149859497324</v>
+        <v>0.48631516809109598</v>
       </c>
       <c r="I19" s="105">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J19" s="87">
         <f t="shared" si="2"/>
@@ -4712,14 +4916,14 @@
       <c r="L19" s="176"/>
       <c r="M19" s="6">
         <f t="shared" si="4"/>
-        <v>324706.48631516809</v>
+        <v>324707.15298183478</v>
       </c>
       <c r="N19" s="10">
         <f t="shared" si="1"/>
-        <v>344188.87549407815</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+        <v>344189.58216074487</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -4734,18 +4938,18 @@
         <v>2.84</v>
       </c>
       <c r="F20" s="87">
-        <v>226252.98919040806</v>
-      </c>
-      <c r="G20" s="196">
-        <f>265290-G38</f>
-        <v>226253.33333333334</v>
+        <v>268852.98919040803</v>
+      </c>
+      <c r="G20" s="195">
+        <f>315240-G38</f>
+        <v>268853.33333333331</v>
       </c>
       <c r="H20" s="126">
         <f t="shared" si="0"/>
         <v>-0.34414292528526857</v>
       </c>
       <c r="I20" s="105">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="87">
         <f t="shared" si="2"/>
@@ -4765,7 +4969,7 @@
         <v>284984.16854183254</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -4780,18 +4984,18 @@
         <v>3.43</v>
       </c>
       <c r="F21" s="87">
-        <v>273256.22197512927</v>
-      </c>
-      <c r="G21" s="196">
-        <f>316276-G45</f>
-        <v>273256</v>
+        <v>324706.88864179596</v>
+      </c>
+      <c r="G21" s="195">
+        <f>375827-G45</f>
+        <v>324707</v>
       </c>
       <c r="H21" s="126">
         <f t="shared" si="0"/>
-        <v>0.2219751292723231</v>
+        <v>-0.11135820404160768</v>
       </c>
       <c r="I21" s="105">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J21" s="87">
         <f t="shared" si="2"/>
@@ -4804,14 +5008,14 @@
       <c r="L21" s="176"/>
       <c r="M21" s="6">
         <f t="shared" si="4"/>
-        <v>324706.88864179596</v>
+        <v>324706.55530846264</v>
       </c>
       <c r="N21" s="10">
         <f t="shared" si="1"/>
-        <v>344189.30196030374</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+        <v>344188.94862697041</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
@@ -4826,18 +5030,18 @@
         <v>2.84</v>
       </c>
       <c r="F22" s="87">
-        <v>226253.33333333334</v>
-      </c>
-      <c r="G22" s="196">
+        <v>268853.33333333331</v>
+      </c>
+      <c r="G22" s="195">
         <f>F22</f>
-        <v>226253.33333333334</v>
+        <v>268853.33333333331</v>
       </c>
       <c r="H22" s="126">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I22" s="105">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J22" s="87">
         <f t="shared" si="2"/>
@@ -4857,7 +5061,7 @@
         <v>284984.53333333333</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>54</v>
       </c>
@@ -4872,15 +5076,18 @@
         <v>3.43</v>
       </c>
       <c r="F23" s="87">
-        <v>291660.88166989514</v>
-      </c>
-      <c r="G23" s="197"/>
+        <v>616367.54833656177</v>
+      </c>
+      <c r="G23" s="196">
+        <f>400000-G46</f>
+        <v>312833.33333333331</v>
+      </c>
       <c r="H23" s="126">
         <f t="shared" si="0"/>
-        <v>291660.88166989514</v>
+        <v>303534.21500322846</v>
       </c>
       <c r="I23" s="105">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J23" s="87">
         <f t="shared" si="2"/>
@@ -4893,14 +5100,14 @@
       <c r="L23" s="176"/>
       <c r="M23" s="6">
         <f t="shared" si="4"/>
-        <v>616367.54833656177</v>
+        <v>628240.88166989514</v>
       </c>
       <c r="N23" s="10">
         <f t="shared" si="1"/>
-        <v>653349.60123675549</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+        <v>665935.33457008889</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>56</v>
       </c>
@@ -4915,18 +5122,18 @@
         <v>2.84</v>
       </c>
       <c r="F24" s="87">
-        <v>230628.70675440805</v>
-      </c>
-      <c r="G24" s="196">
-        <f>270500-G37</f>
-        <v>231463.33333333334</v>
+        <v>288018.70675440802</v>
+      </c>
+      <c r="G24" s="195">
+        <f>335000-G37</f>
+        <v>288613.33333333331</v>
       </c>
       <c r="H24" s="126">
         <f t="shared" si="0"/>
-        <v>-834.62657892529387</v>
+        <v>-594.62657892529387</v>
       </c>
       <c r="I24" s="161">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J24" s="87">
         <f t="shared" si="2"/>
@@ -4936,19 +5143,17 @@
         <f t="shared" si="3"/>
         <v>241400</v>
       </c>
-      <c r="L24" s="176">
-        <v>20000</v>
-      </c>
+      <c r="L24" s="176"/>
       <c r="M24" s="6">
         <f t="shared" si="4"/>
-        <v>288018.70675440802</v>
+        <v>268258.70675440802</v>
       </c>
       <c r="N24" s="10">
         <f t="shared" si="1"/>
-        <v>305299.82915967249</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+        <v>284354.22915967251</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
@@ -4963,18 +5168,18 @@
         <v>3.43</v>
       </c>
       <c r="F25" s="87">
-        <v>273256.33333333349</v>
-      </c>
-      <c r="G25" s="197">
-        <f>273856</f>
-        <v>273856</v>
+        <v>411572.00000000017</v>
+      </c>
+      <c r="G25" s="196">
+        <f>F25</f>
+        <v>411572.00000000017</v>
       </c>
       <c r="H25" s="126">
         <f t="shared" si="0"/>
-        <v>-599.66666666651145</v>
+        <v>0</v>
       </c>
       <c r="I25" s="105">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J25" s="87">
         <f t="shared" si="2"/>
@@ -4985,22 +5190,21 @@
         <v>291550</v>
       </c>
       <c r="L25" s="177">
-        <f>K25*0.3</f>
-        <v>87465</v>
+        <v>20000</v>
       </c>
       <c r="M25" s="6">
         <f t="shared" si="4"/>
-        <v>411572.00000000017</v>
+        <v>344706.66666666669</v>
       </c>
       <c r="N25" s="10">
         <f t="shared" si="1"/>
-        <v>436266.32000000018</v>
+        <v>365389.06666666671</v>
       </c>
       <c r="P25" s="133"/>
       <c r="Q25" s="133"/>
       <c r="R25" s="133"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>59</v>
       </c>
@@ -5015,18 +5219,18 @@
         <v>6</v>
       </c>
       <c r="F26" s="87">
-        <v>366291.99266603705</v>
-      </c>
-      <c r="G26" s="197">
-        <f>1000000-G36-G30-G31</f>
-        <v>873330</v>
+        <v>60961.992666037055</v>
+      </c>
+      <c r="G26" s="196">
+        <f>1000000+800000-G36-G30-G31</f>
+        <v>1649480</v>
       </c>
       <c r="H26" s="127">
         <f t="shared" si="0"/>
-        <v>-507038.00733396295</v>
+        <v>-1588518.0073339629</v>
       </c>
       <c r="I26" s="105">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26" s="87">
         <f t="shared" si="2"/>
@@ -5039,14 +5243,14 @@
       <c r="L26" s="176"/>
       <c r="M26" s="6">
         <f t="shared" si="4"/>
-        <v>60961.992666037055</v>
+        <v>-1020518.0073339629</v>
       </c>
       <c r="N26" s="10">
         <f t="shared" si="1"/>
-        <v>64619.712225999276</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+        <v>-1081749.0877740008</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>61</v>
       </c>
@@ -5061,18 +5265,18 @@
         <v>5.89</v>
       </c>
       <c r="F27" s="87">
-        <v>469107.037951932</v>
-      </c>
-      <c r="G27" s="196">
-        <f>561420-G39-G40</f>
-        <v>469006.66666666669</v>
+        <v>557687.03795193194</v>
+      </c>
+      <c r="G27" s="195">
+        <f>674089-G39-G40</f>
+        <v>564275.66666666663</v>
       </c>
       <c r="H27" s="126">
         <f t="shared" si="0"/>
-        <v>100.3712852653116</v>
+        <v>-6588.6287147346884</v>
       </c>
       <c r="I27" s="105">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J27" s="87">
         <f t="shared" si="2"/>
@@ -5085,15 +5289,15 @@
       <c r="L27" s="176"/>
       <c r="M27" s="6">
         <f t="shared" si="4"/>
-        <v>557687.03795193194</v>
+        <v>550998.03795193194</v>
       </c>
       <c r="N27" s="10">
         <f t="shared" si="1"/>
-        <v>591148.26022904785</v>
+        <v>584057.92022904789</v>
       </c>
       <c r="R27" s="133"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>63</v>
       </c>
@@ -5108,15 +5312,15 @@
         <v>5.89</v>
       </c>
       <c r="F28" s="87">
-        <v>468694.50782654091</v>
-      </c>
-      <c r="G28" s="196">
-        <f>554000-G32-G33</f>
-        <v>469553.33333333331</v>
+        <v>556727.84115987422</v>
+      </c>
+      <c r="G28" s="195">
+        <f>658000-G32-G33</f>
+        <v>557653.33333333337</v>
       </c>
       <c r="H28" s="126">
         <f t="shared" si="0"/>
-        <v>-858.82550679240376</v>
+        <v>-925.49217345914803</v>
       </c>
       <c r="I28" s="105">
         <v>12</v>
@@ -5132,14 +5336,14 @@
       <c r="L28" s="176"/>
       <c r="M28" s="6">
         <f t="shared" si="4"/>
-        <v>556727.84115987422</v>
+        <v>556661.17449320748</v>
       </c>
       <c r="N28" s="10">
         <f t="shared" si="1"/>
-        <v>590131.51162946667</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+        <v>590060.84496279992</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -5154,19 +5358,14 @@
         <v>5.89</v>
       </c>
       <c r="F29" s="87">
-        <v>938383.0372900333</v>
-      </c>
-      <c r="G29" s="197">
-        <f>1194909-G42-G43-G44</f>
-        <v>938382.33333333337</v>
-      </c>
+        <v>557587.37062336656</v>
+      </c>
+      <c r="G29" s="196"/>
       <c r="H29" s="127">
         <f t="shared" si="0"/>
-        <v>0.70395669993013144</v>
-      </c>
-      <c r="I29" s="105">
-        <v>15</v>
-      </c>
+        <v>557587.37062336656</v>
+      </c>
+      <c r="I29" s="105"/>
       <c r="J29" s="87">
         <f t="shared" si="2"/>
         <v>56936.666666666657</v>
@@ -5178,14 +5377,14 @@
       <c r="L29" s="176"/>
       <c r="M29" s="6">
         <f t="shared" si="4"/>
-        <v>557587.37062336656</v>
+        <v>1115174.0372900332</v>
       </c>
       <c r="N29" s="10">
         <f t="shared" si="1"/>
-        <v>591042.61286076857</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+        <v>1182084.4795274353</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="122" t="s">
         <v>96</v>
       </c>
@@ -5200,11 +5399,11 @@
         <v>0.54</v>
       </c>
       <c r="F30" s="87">
-        <v>43020.000000000007</v>
-      </c>
-      <c r="G30" s="196">
+        <v>51120</v>
+      </c>
+      <c r="G30" s="195">
         <f>F30</f>
-        <v>43020.000000000007</v>
+        <v>51120</v>
       </c>
       <c r="H30" s="126">
         <f t="shared" si="0"/>
@@ -5229,7 +5428,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="122" t="s">
         <v>96</v>
       </c>
@@ -5244,11 +5443,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F31" s="87">
-        <v>43816.666666666672</v>
-      </c>
-      <c r="G31" s="196">
+        <v>52066.666666666664</v>
+      </c>
+      <c r="G31" s="195">
         <f>F31</f>
-        <v>43816.666666666672</v>
+        <v>52066.666666666664</v>
       </c>
       <c r="H31" s="126">
         <f t="shared" si="0"/>
@@ -5273,7 +5472,7 @@
         <v>55190.666666666664</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="122" t="s">
         <v>96</v>
       </c>
@@ -5288,11 +5487,11 @@
         <v>0.45</v>
       </c>
       <c r="F32" s="87">
-        <v>35850</v>
-      </c>
-      <c r="G32" s="196">
+        <v>42600</v>
+      </c>
+      <c r="G32" s="195">
         <f>F32</f>
-        <v>35850</v>
+        <v>42600</v>
       </c>
       <c r="H32" s="126">
         <f t="shared" si="0"/>
@@ -5317,7 +5516,7 @@
         <v>45156</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="122" t="s">
         <v>96</v>
       </c>
@@ -5332,11 +5531,11 @@
         <v>0.61</v>
       </c>
       <c r="F33" s="87">
-        <v>48596.666666666664</v>
-      </c>
-      <c r="G33" s="196">
+        <v>57746.666666666664</v>
+      </c>
+      <c r="G33" s="195">
         <f t="shared" ref="G33:G34" si="5">F33</f>
-        <v>48596.666666666664</v>
+        <v>57746.666666666664</v>
       </c>
       <c r="H33" s="126">
         <f t="shared" si="0"/>
@@ -5361,7 +5560,7 @@
         <v>61211.466666666667</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="122" t="s">
         <v>96</v>
       </c>
@@ -5376,11 +5575,11 @@
         <v>0.54</v>
       </c>
       <c r="F34" s="87">
-        <v>43020.000000000007</v>
-      </c>
-      <c r="G34" s="196">
+        <v>51120</v>
+      </c>
+      <c r="G34" s="195">
         <f t="shared" si="5"/>
-        <v>43020.000000000007</v>
+        <v>51120</v>
       </c>
       <c r="H34" s="126">
         <f t="shared" si="0"/>
@@ -5405,7 +5604,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="122" t="s">
         <v>96</v>
       </c>
@@ -5414,21 +5613,18 @@
         <v>6</v>
       </c>
       <c r="D35" s="128" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E35" s="7">
         <v>0.5</v>
       </c>
-      <c r="F35" s="10">
-        <v>39833.333333333336</v>
-      </c>
-      <c r="G35" s="197">
-        <f>F35</f>
-        <v>39833.333333333336</v>
-      </c>
+      <c r="F35" s="6">
+        <v>47333.333333333336</v>
+      </c>
+      <c r="G35" s="196"/>
       <c r="H35" s="126">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>47333.333333333336</v>
       </c>
       <c r="I35" s="105"/>
       <c r="J35" s="87">
@@ -5442,14 +5638,14 @@
       <c r="L35" s="150"/>
       <c r="M35" s="6">
         <f t="shared" si="4"/>
-        <v>47333.333333333336</v>
+        <v>94666.666666666672</v>
       </c>
       <c r="N35" s="10">
         <f t="shared" si="1"/>
-        <v>50173.333333333336</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>100346.66666666667</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="122" t="s">
         <v>96</v>
       </c>
@@ -5464,11 +5660,11 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="87">
-        <v>39833.333333333336</v>
-      </c>
-      <c r="G36" s="196">
+        <v>47333.333333333336</v>
+      </c>
+      <c r="G36" s="195">
         <f>F36</f>
-        <v>39833.333333333336</v>
+        <v>47333.333333333336</v>
       </c>
       <c r="H36" s="126">
         <f t="shared" si="0"/>
@@ -5493,7 +5689,7 @@
         <v>50173.333333333336</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="122" t="s">
         <v>96</v>
       </c>
@@ -5508,11 +5704,11 @@
         <v>0.49</v>
       </c>
       <c r="F37" s="87">
-        <v>39036.666666666664</v>
-      </c>
-      <c r="G37" s="196">
+        <v>46386.666666666664</v>
+      </c>
+      <c r="G37" s="195">
         <f t="shared" ref="G37:G41" si="6">F37</f>
-        <v>39036.666666666664</v>
+        <v>46386.666666666664</v>
       </c>
       <c r="H37" s="126">
         <f t="shared" si="0"/>
@@ -5537,7 +5733,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="122" t="s">
         <v>96</v>
       </c>
@@ -5552,11 +5748,11 @@
         <v>0.49</v>
       </c>
       <c r="F38" s="87">
-        <v>39036.666666666664</v>
-      </c>
-      <c r="G38" s="196">
+        <v>46386.666666666664</v>
+      </c>
+      <c r="G38" s="195">
         <f t="shared" si="6"/>
-        <v>39036.666666666664</v>
+        <v>46386.666666666664</v>
       </c>
       <c r="H38" s="126">
         <f t="shared" si="0"/>
@@ -5581,7 +5777,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="122" t="s">
         <v>96</v>
       </c>
@@ -5596,11 +5792,11 @@
         <v>0.59</v>
       </c>
       <c r="F39" s="87">
-        <v>47003.333333333336</v>
-      </c>
-      <c r="G39" s="196">
+        <v>55853.333333333336</v>
+      </c>
+      <c r="G39" s="195">
         <f t="shared" si="6"/>
-        <v>47003.333333333336</v>
+        <v>55853.333333333336</v>
       </c>
       <c r="H39" s="126">
         <f t="shared" si="0"/>
@@ -5625,7 +5821,7 @@
         <v>59204.533333333333</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="122" t="s">
         <v>96</v>
       </c>
@@ -5640,11 +5836,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F40" s="87">
-        <v>45409.999999999993</v>
-      </c>
-      <c r="G40" s="196">
+        <v>53960</v>
+      </c>
+      <c r="G40" s="195">
         <f t="shared" si="6"/>
-        <v>45409.999999999993</v>
+        <v>53960</v>
       </c>
       <c r="H40" s="126">
         <f t="shared" si="0"/>
@@ -5669,7 +5865,7 @@
         <v>57197.599999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="122" t="s">
         <v>96</v>
       </c>
@@ -5684,11 +5880,11 @@
         <v>0.54</v>
       </c>
       <c r="F41" s="87">
-        <v>43020.000000000007</v>
-      </c>
-      <c r="G41" s="196">
+        <v>51120</v>
+      </c>
+      <c r="G41" s="195">
         <f t="shared" si="6"/>
-        <v>43020.000000000007</v>
+        <v>51120</v>
       </c>
       <c r="H41" s="126">
         <f t="shared" si="0"/>
@@ -5713,7 +5909,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="122" t="s">
         <v>96</v>
       </c>
@@ -5728,15 +5924,12 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F42" s="87">
-        <v>87633.333333333343</v>
-      </c>
-      <c r="G42" s="196">
-        <f>F42</f>
-        <v>87633.333333333343</v>
-      </c>
+        <v>52066.666666666664</v>
+      </c>
+      <c r="G42" s="195"/>
       <c r="H42" s="126">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>52066.666666666664</v>
       </c>
       <c r="I42" s="105"/>
       <c r="J42" s="87">
@@ -5750,14 +5943,14 @@
       <c r="L42" s="150"/>
       <c r="M42" s="6">
         <f t="shared" si="4"/>
-        <v>52066.666666666664</v>
+        <v>104133.33333333333</v>
       </c>
       <c r="N42" s="10">
         <f t="shared" si="1"/>
-        <v>55190.666666666664</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+        <v>110381.33333333333</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="122" t="s">
         <v>96</v>
       </c>
@@ -5772,15 +5965,12 @@
         <v>0.45</v>
       </c>
       <c r="F43" s="87">
-        <v>71700</v>
-      </c>
-      <c r="G43" s="196">
-        <f t="shared" ref="G43:G44" si="7">F43</f>
-        <v>71700</v>
-      </c>
+        <v>42600</v>
+      </c>
+      <c r="G43" s="195"/>
       <c r="H43" s="126">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42600</v>
       </c>
       <c r="I43" s="105"/>
       <c r="J43" s="87">
@@ -5794,18 +5984,18 @@
       <c r="L43" s="150"/>
       <c r="M43" s="6">
         <f t="shared" si="4"/>
-        <v>42600</v>
+        <v>85200</v>
       </c>
       <c r="N43" s="10">
         <f t="shared" si="1"/>
-        <v>45156</v>
+        <v>90312</v>
       </c>
       <c r="P43" s="107">
         <f>L1-K52</f>
-        <v>707741.61314300075</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>64417.213143000379</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="122" t="s">
         <v>96</v>
       </c>
@@ -5820,15 +6010,12 @@
         <v>0.61</v>
       </c>
       <c r="F44" s="87">
-        <v>97193.333333333328</v>
-      </c>
-      <c r="G44" s="196">
-        <f t="shared" si="7"/>
-        <v>97193.333333333328</v>
-      </c>
+        <v>57746.666666666664</v>
+      </c>
+      <c r="G44" s="195"/>
       <c r="H44" s="126">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>57746.666666666664</v>
       </c>
       <c r="I44" s="105"/>
       <c r="J44" s="87">
@@ -5842,14 +6029,14 @@
       <c r="L44" s="150"/>
       <c r="M44" s="6">
         <f t="shared" si="4"/>
-        <v>57746.666666666664</v>
+        <v>115493.33333333333</v>
       </c>
       <c r="N44" s="10">
         <f t="shared" si="1"/>
-        <v>61211.466666666667</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+        <v>122422.93333333333</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="122" t="s">
         <v>96</v>
       </c>
@@ -5864,11 +6051,11 @@
         <v>0.54</v>
       </c>
       <c r="F45" s="87">
-        <v>43020.000000000007</v>
-      </c>
-      <c r="G45" s="196">
-        <f t="shared" ref="G45:G48" si="8">F45</f>
-        <v>43020.000000000007</v>
+        <v>51120</v>
+      </c>
+      <c r="G45" s="195">
+        <f t="shared" ref="G45" si="7">F45</f>
+        <v>51120</v>
       </c>
       <c r="H45" s="126">
         <f t="shared" si="0"/>
@@ -5893,7 +6080,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="122" t="s">
         <v>96</v>
       </c>
@@ -5908,12 +6095,15 @@
         <v>0.5</v>
       </c>
       <c r="F46" s="87">
-        <v>39833.333333333336</v>
-      </c>
-      <c r="G46" s="196"/>
+        <v>87166.666666666672</v>
+      </c>
+      <c r="G46" s="195">
+        <f t="shared" ref="G46:G51" si="8">F46</f>
+        <v>87166.666666666672</v>
+      </c>
       <c r="H46" s="126">
         <f t="shared" si="0"/>
-        <v>39833.333333333336</v>
+        <v>0</v>
       </c>
       <c r="I46" s="105"/>
       <c r="J46" s="87">
@@ -5927,17 +6117,17 @@
       <c r="L46" s="150"/>
       <c r="M46" s="6">
         <f t="shared" si="4"/>
-        <v>87166.666666666672</v>
+        <v>47333.333333333336</v>
       </c>
       <c r="N46" s="10">
         <f t="shared" si="1"/>
-        <v>92396.666666666672</v>
+        <v>50173.333333333336</v>
       </c>
       <c r="Q46" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="122" t="s">
         <v>96</v>
       </c>
@@ -5952,11 +6142,11 @@
         <v>0.5</v>
       </c>
       <c r="F47" s="87">
-        <v>39833.333333333336</v>
-      </c>
-      <c r="G47" s="196">
+        <v>47333.333333333336</v>
+      </c>
+      <c r="G47" s="195">
         <f t="shared" si="8"/>
-        <v>39833.333333333336</v>
+        <v>47333.333333333336</v>
       </c>
       <c r="H47" s="126">
         <f t="shared" si="0"/>
@@ -5986,7 +6176,7 @@
         <v>-888463.33333333314</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="122" t="s">
         <v>96</v>
       </c>
@@ -6001,11 +6191,11 @@
         <v>0.49</v>
       </c>
       <c r="F48" s="87">
-        <v>39036.666666666664</v>
-      </c>
-      <c r="G48" s="196">
+        <v>46386.666666666664</v>
+      </c>
+      <c r="G48" s="195">
         <f t="shared" si="8"/>
-        <v>39036.666666666664</v>
+        <v>46386.666666666664</v>
       </c>
       <c r="H48" s="126">
         <f t="shared" si="0"/>
@@ -6030,7 +6220,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="122" t="s">
         <v>96</v>
       </c>
@@ -6046,11 +6236,11 @@
         <v>0.49</v>
       </c>
       <c r="F49" s="87">
-        <v>39036.666666666664</v>
-      </c>
-      <c r="G49" s="196">
-        <f>F49</f>
-        <v>39036.666666666664</v>
+        <v>49169.866666666661</v>
+      </c>
+      <c r="G49" s="195">
+        <f t="shared" si="8"/>
+        <v>49169.866666666661</v>
       </c>
       <c r="H49" s="126">
         <f t="shared" si="0"/>
@@ -6075,7 +6265,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="122" t="s">
         <v>96</v>
       </c>
@@ -6090,11 +6280,11 @@
         <v>0.59</v>
       </c>
       <c r="F50" s="87">
-        <v>47003.333333333336</v>
-      </c>
-      <c r="G50" s="197">
-        <f>F50</f>
-        <v>47003.333333333336</v>
+        <v>55853.333333333336</v>
+      </c>
+      <c r="G50" s="196">
+        <f t="shared" si="8"/>
+        <v>55853.333333333336</v>
       </c>
       <c r="H50" s="126">
         <f t="shared" si="0"/>
@@ -6119,7 +6309,7 @@
         <v>59204.533333333333</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="122" t="s">
         <v>96</v>
       </c>
@@ -6134,11 +6324,11 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F51" s="87">
-        <v>45409.999999999993</v>
-      </c>
-      <c r="G51" s="196">
-        <f>F51</f>
-        <v>45409.999999999993</v>
+        <v>53960</v>
+      </c>
+      <c r="G51" s="195">
+        <f t="shared" si="8"/>
+        <v>53960</v>
       </c>
       <c r="H51" s="126">
         <f t="shared" si="0"/>
@@ -6163,7 +6353,7 @@
         <v>57197.599999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="88"/>
       <c r="B52" s="88"/>
       <c r="C52" s="88"/>
@@ -6174,11 +6364,11 @@
       </c>
       <c r="F52" s="173">
         <f>SUM(F7:F51)</f>
-        <v>8247204.8163158055</v>
+        <v>9301106.3575824741</v>
       </c>
       <c r="G52" s="173">
         <f>SUM(G7:G51)</f>
-        <v>8413417.1728006657</v>
+        <v>9493696.4535236657</v>
       </c>
       <c r="H52" s="88"/>
       <c r="I52" s="88"/>
@@ -6192,53 +6382,53 @@
       </c>
       <c r="L52" s="175">
         <f>SUM(L7:L51)</f>
-        <v>107465</v>
+        <v>40000</v>
       </c>
       <c r="M52" s="90">
         <f>SUM(M7:M51)</f>
-        <v>9265298.7637054734</v>
+        <v>9171456.024249142</v>
       </c>
       <c r="N52" s="89">
         <f>SUM(N7:N51)</f>
-        <v>9821216.6895278003</v>
+        <v>9721743.3857040871</v>
       </c>
       <c r="P52" s="130"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="133">
         <f>K52-L1</f>
-        <v>-707741.61314300075</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="228"/>
-      <c r="D54" s="228"/>
-      <c r="E54" s="228"/>
-      <c r="F54" s="228"/>
-      <c r="G54" s="228"/>
-      <c r="H54" s="228"/>
-      <c r="I54" s="228"/>
-      <c r="J54" s="228"/>
-      <c r="K54" s="228"/>
-      <c r="L54" s="228"/>
-      <c r="M54" s="228"/>
-      <c r="N54" s="228"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="228"/>
-      <c r="D55" s="228"/>
-      <c r="E55" s="228"/>
-      <c r="F55" s="228"/>
-      <c r="G55" s="228"/>
-      <c r="H55" s="228"/>
-      <c r="I55" s="228"/>
-      <c r="J55" s="228"/>
-      <c r="K55" s="228"/>
-      <c r="L55" s="228"/>
-      <c r="M55" s="228"/>
-      <c r="N55" s="228"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+        <v>-64417.213143000379</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="263"/>
+      <c r="D54" s="263"/>
+      <c r="E54" s="263"/>
+      <c r="F54" s="263"/>
+      <c r="G54" s="263"/>
+      <c r="H54" s="263"/>
+      <c r="I54" s="263"/>
+      <c r="J54" s="263"/>
+      <c r="K54" s="263"/>
+      <c r="L54" s="263"/>
+      <c r="M54" s="263"/>
+      <c r="N54" s="263"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="263"/>
+      <c r="D55" s="263"/>
+      <c r="E55" s="263"/>
+      <c r="F55" s="263"/>
+      <c r="G55" s="263"/>
+      <c r="H55" s="263"/>
+      <c r="I55" s="263"/>
+      <c r="J55" s="263"/>
+      <c r="K55" s="263"/>
+      <c r="L55" s="263"/>
+      <c r="M55" s="263"/>
+      <c r="N55" s="263"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="152"/>
       <c r="D56" s="152"/>
       <c r="E56" s="152"/>
@@ -6252,112 +6442,108 @@
       <c r="M56" s="152"/>
       <c r="N56" s="152"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="228" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C57" s="263" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="228"/>
-      <c r="E57" s="228"/>
-      <c r="F57" s="228"/>
-      <c r="G57" s="228"/>
-      <c r="H57" s="228"/>
-      <c r="I57" s="228"/>
-      <c r="J57" s="228"/>
-      <c r="K57" s="228"/>
-      <c r="L57" s="228"/>
-      <c r="M57" s="228"/>
-      <c r="N57" s="228"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="228"/>
-      <c r="D58" s="228"/>
-      <c r="E58" s="228"/>
-      <c r="F58" s="228"/>
-      <c r="G58" s="228"/>
-      <c r="H58" s="228"/>
-      <c r="I58" s="228"/>
-      <c r="J58" s="228"/>
-      <c r="K58" s="228"/>
-      <c r="L58" s="228"/>
-      <c r="M58" s="228"/>
-      <c r="N58" s="228"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="228"/>
-      <c r="D59" s="228"/>
-      <c r="E59" s="228"/>
-      <c r="F59" s="228"/>
-      <c r="G59" s="228"/>
-      <c r="H59" s="228"/>
-      <c r="I59" s="228"/>
-      <c r="J59" s="228"/>
-      <c r="K59" s="228"/>
-      <c r="L59" s="228"/>
-      <c r="M59" s="228"/>
-      <c r="N59" s="228"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="228"/>
-      <c r="D60" s="228"/>
-      <c r="E60" s="228"/>
-      <c r="F60" s="228"/>
-      <c r="G60" s="228"/>
-      <c r="H60" s="228"/>
-      <c r="I60" s="228"/>
-      <c r="J60" s="228"/>
-      <c r="K60" s="228"/>
-      <c r="L60" s="228"/>
-      <c r="M60" s="228"/>
-      <c r="N60" s="228"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="228"/>
-      <c r="D61" s="228"/>
-      <c r="E61" s="228"/>
-      <c r="F61" s="228"/>
-      <c r="G61" s="228"/>
-      <c r="H61" s="228"/>
-      <c r="I61" s="228"/>
-      <c r="J61" s="228"/>
-      <c r="K61" s="228"/>
-      <c r="L61" s="228"/>
-      <c r="M61" s="228"/>
-      <c r="N61" s="228"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="228"/>
-      <c r="D62" s="228"/>
-      <c r="E62" s="228"/>
-      <c r="F62" s="228"/>
-      <c r="G62" s="228"/>
-      <c r="H62" s="228"/>
-      <c r="I62" s="228"/>
-      <c r="J62" s="228"/>
-      <c r="K62" s="228"/>
-      <c r="L62" s="228"/>
-      <c r="M62" s="228"/>
-      <c r="N62" s="228"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="228"/>
-      <c r="D63" s="228"/>
-      <c r="E63" s="228"/>
-      <c r="F63" s="228"/>
-      <c r="G63" s="228"/>
-      <c r="H63" s="228"/>
-      <c r="I63" s="228"/>
-      <c r="J63" s="228"/>
-      <c r="K63" s="228"/>
-      <c r="L63" s="228"/>
-      <c r="M63" s="228"/>
-      <c r="N63" s="228"/>
+      <c r="D57" s="263"/>
+      <c r="E57" s="263"/>
+      <c r="F57" s="263"/>
+      <c r="G57" s="263"/>
+      <c r="H57" s="263"/>
+      <c r="I57" s="263"/>
+      <c r="J57" s="263"/>
+      <c r="K57" s="263"/>
+      <c r="L57" s="263"/>
+      <c r="M57" s="263"/>
+      <c r="N57" s="263"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C58" s="263"/>
+      <c r="D58" s="263"/>
+      <c r="E58" s="263"/>
+      <c r="F58" s="263"/>
+      <c r="G58" s="263"/>
+      <c r="H58" s="263"/>
+      <c r="I58" s="263"/>
+      <c r="J58" s="263"/>
+      <c r="K58" s="263"/>
+      <c r="L58" s="263"/>
+      <c r="M58" s="263"/>
+      <c r="N58" s="263"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C59" s="263"/>
+      <c r="D59" s="263"/>
+      <c r="E59" s="263"/>
+      <c r="F59" s="263"/>
+      <c r="G59" s="263"/>
+      <c r="H59" s="263"/>
+      <c r="I59" s="263"/>
+      <c r="J59" s="263"/>
+      <c r="K59" s="263"/>
+      <c r="L59" s="263"/>
+      <c r="M59" s="263"/>
+      <c r="N59" s="263"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C60" s="263"/>
+      <c r="D60" s="263"/>
+      <c r="E60" s="263"/>
+      <c r="F60" s="263"/>
+      <c r="G60" s="263"/>
+      <c r="H60" s="263"/>
+      <c r="I60" s="263"/>
+      <c r="J60" s="263"/>
+      <c r="K60" s="263"/>
+      <c r="L60" s="263"/>
+      <c r="M60" s="263"/>
+      <c r="N60" s="263"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C61" s="263"/>
+      <c r="D61" s="263"/>
+      <c r="E61" s="263"/>
+      <c r="F61" s="263"/>
+      <c r="G61" s="263"/>
+      <c r="H61" s="263"/>
+      <c r="I61" s="263"/>
+      <c r="J61" s="263"/>
+      <c r="K61" s="263"/>
+      <c r="L61" s="263"/>
+      <c r="M61" s="263"/>
+      <c r="N61" s="263"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C62" s="263"/>
+      <c r="D62" s="263"/>
+      <c r="E62" s="263"/>
+      <c r="F62" s="263"/>
+      <c r="G62" s="263"/>
+      <c r="H62" s="263"/>
+      <c r="I62" s="263"/>
+      <c r="J62" s="263"/>
+      <c r="K62" s="263"/>
+      <c r="L62" s="263"/>
+      <c r="M62" s="263"/>
+      <c r="N62" s="263"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C63" s="263"/>
+      <c r="D63" s="263"/>
+      <c r="E63" s="263"/>
+      <c r="F63" s="263"/>
+      <c r="G63" s="263"/>
+      <c r="H63" s="263"/>
+      <c r="I63" s="263"/>
+      <c r="J63" s="263"/>
+      <c r="K63" s="263"/>
+      <c r="L63" s="263"/>
+      <c r="M63" s="263"/>
+      <c r="N63" s="263"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
@@ -6372,6 +6558,10 @@
     <mergeCell ref="A1:J4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6381,88 +6571,88 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596D2FF5-218B-41A1-9BCB-F43114942886}">
   <dimension ref="C4:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
-        <v>143</v>
       </c>
       <c r="D5" s="168">
         <v>-447223.45918396302</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>144</v>
       </c>
-      <c r="D6" s="168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
+      <c r="D7" s="168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C8" t="s">
-        <v>146</v>
-      </c>
       <c r="D8" s="168">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C10" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D11" s="168">
         <v>451182</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D12" s="168">
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D13" s="168">
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D14" s="168">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C16" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -6470,67 +6660,67 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D17" s="168">
         <f>D11+D5</f>
         <v>3958.5408160369843</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D18" s="168">
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D19" s="168">
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D20" s="168">
         <v>37598.5</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D21" s="168">
         <v>-25000</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C22" s="252" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="255">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="264" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="267">
         <f>SUM(D17:D21)</f>
         <v>98521.770816036995</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C23" s="253"/>
-      <c r="D23" s="256"/>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C24" s="253"/>
-      <c r="D24" s="256"/>
-    </row>
-    <row r="25" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="254"/>
-      <c r="D25" s="257"/>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="265"/>
+      <c r="D23" s="268"/>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="265"/>
+      <c r="D24" s="268"/>
+    </row>
+    <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="266"/>
+      <c r="D25" s="269"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6545,16 +6735,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -6578,7 +6768,7 @@
       </c>
       <c r="O1" s="51"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="48"/>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
@@ -6597,7 +6787,7 @@
       <c r="N2" s="48"/>
       <c r="O2" s="48"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="48"/>
       <c r="B3" s="50"/>
       <c r="C3" s="50"/>
@@ -6620,7 +6810,7 @@
       </c>
       <c r="O3" s="53"/>
     </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="48"/>
       <c r="B4" s="50"/>
       <c r="C4" s="50"/>
@@ -6641,11 +6831,11 @@
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
     </row>
-    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="258" t="s">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="270" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="258" t="s">
+      <c r="B5" s="270" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="54" t="s">
@@ -6657,7 +6847,7 @@
       <c r="E5" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="258" t="s">
+      <c r="F5" s="270" t="s">
         <v>75</v>
       </c>
       <c r="G5" s="36" t="s">
@@ -6679,16 +6869,16 @@
         <v>29</v>
       </c>
       <c r="M5" s="40"/>
-      <c r="N5" s="258" t="s">
+      <c r="N5" s="270" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="258" t="s">
+      <c r="O5" s="270" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="259"/>
-      <c r="B6" s="259"/>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="271"/>
+      <c r="B6" s="271"/>
       <c r="C6" s="55" t="s">
         <v>80</v>
       </c>
@@ -6698,7 +6888,7 @@
       <c r="E6" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="259"/>
+      <c r="F6" s="271"/>
       <c r="G6" s="43" t="s">
         <v>81</v>
       </c>
@@ -6718,10 +6908,10 @@
         <v>84</v>
       </c>
       <c r="M6" s="46"/>
-      <c r="N6" s="259"/>
-      <c r="O6" s="259"/>
-    </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="271"/>
+      <c r="O6" s="271"/>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>1</v>
       </c>
@@ -6767,7 +6957,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>2</v>
       </c>
@@ -6813,7 +7003,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>3</v>
       </c>
@@ -6859,7 +7049,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>4</v>
       </c>
@@ -6905,7 +7095,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>5</v>
       </c>
@@ -6951,7 +7141,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>6</v>
       </c>
@@ -6997,7 +7187,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>7</v>
       </c>
@@ -7043,7 +7233,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>8</v>
       </c>
@@ -7089,7 +7279,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>9</v>
       </c>
@@ -7135,7 +7325,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>10</v>
       </c>
@@ -7181,7 +7371,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>11</v>
       </c>
@@ -7227,7 +7417,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>12</v>
       </c>
@@ -7273,7 +7463,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>13</v>
       </c>
@@ -7319,7 +7509,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>14</v>
       </c>
@@ -7365,7 +7555,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>15</v>
       </c>
@@ -7411,7 +7601,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>16</v>
       </c>
@@ -7457,7 +7647,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>17</v>
       </c>
@@ -7503,7 +7693,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>18</v>
       </c>
@@ -7549,7 +7739,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>19</v>
       </c>
@@ -7595,7 +7785,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>20</v>
       </c>
@@ -7641,7 +7831,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>21</v>
       </c>
@@ -7687,7 +7877,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>22</v>
       </c>
@@ -7733,7 +7923,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
@@ -7750,7 +7940,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12"/>
       <c r="B30" s="13"/>
       <c r="C30" s="56">
@@ -7791,7 +7981,7 @@
         <v>264873.42966686888</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E33" s="32"/>
       <c r="F33" s="32"/>
     </row>
